--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="n">
         <v>3.45</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
         <v>1.9</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1398,7 +1398,7 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1407,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1419,13 +1419,13 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>15.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
         <v>42</v>
@@ -1440,31 +1440,31 @@
         <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF4" t="n">
         <v>27</v>
       </c>
       <c r="AG4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK4" t="n">
         <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
         <v>28</v>
@@ -1479,7 +1479,7 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AS4" t="n">
         <v>3.85</v>
@@ -1488,19 +1488,19 @@
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
         <v>11.5</v>
@@ -1509,7 +1509,7 @@
         <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
         <v>3.85</v>
@@ -1524,7 +1524,7 @@
         <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
         <v>4.1</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 01:06:29</t>
+          <t>2026-06-20 03:22:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
         <v>2.24</v>
@@ -866,7 +866,7 @@
         <v>3.45</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.65</v>
@@ -887,10 +887,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 03:22:38</t>
+          <t>2026-06-20 05:38:58</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 03:22:38</t>
+          <t>2026-06-20 05:38:58</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="I4" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
@@ -1398,7 +1398,7 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1407,10 +1407,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -1419,13 +1419,13 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
         <v>15.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
         <v>42</v>
@@ -1440,31 +1440,31 @@
         <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF4" t="n">
         <v>27</v>
       </c>
       <c r="AG4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
         <v>38</v>
       </c>
       <c r="AL4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN4" t="n">
         <v>28</v>
@@ -1479,7 +1479,7 @@
         <v>11</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS4" t="n">
         <v>3.85</v>
@@ -1488,19 +1488,19 @@
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>11.5</v>
@@ -1509,7 +1509,7 @@
         <v>3.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC4" t="n">
         <v>3.85</v>
@@ -1524,7 +1524,7 @@
         <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 03:22:38</t>
+          <t>2026-06-20 05:38:58</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 03:22:38</t>
+          <t>2026-06-20 05:38:58</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
         <v>4.1</v>
@@ -1882,13 +1882,13 @@
         <v>2.28</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J6" t="n">
         <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 03:22:38</t>
+          <t>2026-06-20 05:38:58</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 03:22:38</t>
+          <t>2026-06-20 05:38:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 05:38:58</t>
+          <t>2026-06-20 07:56:07</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 05:38:58</t>
+          <t>2026-06-20 07:56:07</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
@@ -1395,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
         <v>15.5</v>
@@ -1428,10 +1428,10 @@
         <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
@@ -1443,7 +1443,7 @@
         <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG4" t="n">
         <v>16</v>
@@ -1464,40 +1464,40 @@
         <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN4" t="n">
         <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP4" t="n">
         <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
@@ -1506,25 +1506,25 @@
         <v>11.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>3.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF4" t="n">
         <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 05:38:58</t>
+          <t>2026-06-20 07:56:07</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 05:38:58</t>
+          <t>2026-06-20 07:56:07</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 05:38:58</t>
+          <t>2026-06-20 07:56:07</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 05:38:58</t>
+          <t>2026-06-20 07:56:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 07:56:07</t>
+          <t>2026-06-20 10:13:36</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 07:56:07</t>
+          <t>2026-06-20 10:13:36</t>
         </is>
       </c>
     </row>
@@ -1473,10 +1473,10 @@
         <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
@@ -1488,16 +1488,16 @@
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
         <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 07:56:07</t>
+          <t>2026-06-20 10:13:36</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 07:56:07</t>
+          <t>2026-06-20 10:13:36</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         <v>2.92</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 07:56:07</t>
+          <t>2026-06-20 10:13:36</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 07:56:07</t>
+          <t>2026-06-20 10:13:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 10:13:36</t>
+          <t>2026-06-20 12:30:20</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 10:13:36</t>
+          <t>2026-06-20 12:30:20</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
         <v>13</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
@@ -1488,16 +1488,16 @@
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
         <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 10:13:36</t>
+          <t>2026-06-20 12:30:20</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 10:13:36</t>
+          <t>2026-06-20 12:30:20</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H6" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="I6" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J6" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 10:13:36</t>
+          <t>2026-06-20 12:30:20</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 10:13:36</t>
+          <t>2026-06-20 12:30:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -875,16 +875,16 @@
         <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
         <v>2.12</v>
@@ -893,184 +893,184 @@
         <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BX2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 12:30:20</t>
+          <t>2026-06-20 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1114,31 +1114,31 @@
         <v>1.92</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P3" t="n">
         <v>1.98</v>
@@ -1147,184 +1147,184 @@
         <v>1.89</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 12:30:20</t>
+          <t>2026-06-20 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1383,16 +1383,16 @@
         <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
         <v>2.14</v>
@@ -1401,10 +1401,10 @@
         <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T4" t="n">
         <v>1.64</v>
@@ -1413,10 +1413,10 @@
         <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
         <v>22</v>
@@ -1473,10 +1473,10 @@
         <v>22</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
         <v>13</v>
@@ -1488,16 +1488,16 @@
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW4" t="n">
         <v>18.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.6</v>
@@ -1527,68 +1527,68 @@
         <v>13</v>
       </c>
       <c r="BH4" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BR4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 12:30:20</t>
+          <t>2026-06-20 14:46:33</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 12:30:20</t>
+          <t>2026-06-20 14:46:33</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 12:30:20</t>
+          <t>2026-06-20 14:46:33</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 12:30:20</t>
+          <t>2026-06-20 14:46:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,7 +860,7 @@
         <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H2" t="n">
         <v>3.45</v>
@@ -881,7 +881,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.25</v>
@@ -890,25 +890,25 @@
         <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T2" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X2" t="n">
         <v>25</v>
@@ -965,7 +965,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.24</v>
+        <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>11</v>
@@ -977,13 +977,13 @@
         <v>2.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.14</v>
+        <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.2</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
         <v>2.36</v>
@@ -992,10 +992,10 @@
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.12</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.22</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
         <v>2.36</v>
@@ -1004,7 +1004,7 @@
         <v>2.32</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.28</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
         <v>2.34</v>
@@ -1019,7 +1019,7 @@
         <v>2.46</v>
       </c>
       <c r="BH2" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
         <v>2.64</v>
@@ -1028,49 +1028,49 @@
         <v>13</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.6</v>
+        <v>1.64</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BN2" t="n">
         <v>7.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.72</v>
       </c>
       <c r="BR2" t="n">
         <v>38</v>
       </c>
       <c r="BS2" t="n">
-        <v>15.5</v>
+        <v>1.79</v>
       </c>
       <c r="BT2" t="n">
         <v>10</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV2" t="n">
         <v>38</v>
       </c>
       <c r="BW2" t="n">
-        <v>16</v>
+        <v>1.79</v>
       </c>
       <c r="BX2" t="n">
         <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>20</v>
+        <v>1.81</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
         <v>2.04</v>
@@ -1126,7 +1126,7 @@
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>1.4</v>
@@ -1153,10 +1153,10 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
@@ -1222,7 +1222,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>22</v>
@@ -1243,7 +1243,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
@@ -1261,7 +1261,7 @@
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE3" t="n">
         <v>10.5</v>
@@ -1276,19 +1276,19 @@
         <v>3.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.7</v>
@@ -1300,13 +1300,13 @@
         <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BR3" t="n">
         <v>28</v>
       </c>
       <c r="BS3" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>7.8</v>
@@ -1318,13 +1318,13 @@
         <v>36</v>
       </c>
       <c r="BW3" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BX3" t="n">
         <v>44</v>
       </c>
       <c r="BY3" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
         <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S4" t="n">
         <v>2.5</v>
@@ -1536,13 +1536,13 @@
         <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>21</v>
+        <v>2.92</v>
       </c>
       <c r="BN4" t="n">
         <v>8.800000000000001</v>
@@ -1554,13 +1554,13 @@
         <v>30</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12.5</v>
+        <v>2.68</v>
       </c>
       <c r="BR4" t="n">
         <v>46</v>
       </c>
       <c r="BS4" t="n">
-        <v>17.5</v>
+        <v>2.76</v>
       </c>
       <c r="BT4" t="n">
         <v>8</v>
@@ -1572,30 +1572,30 @@
         <v>26</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>2.64</v>
       </c>
       <c r="BX4" t="n">
         <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>16.5</v>
+        <v>2.74</v>
       </c>
       <c r="BZ4" t="n">
         <v>30</v>
       </c>
       <c r="CA4" t="n">
-        <v>12.5</v>
+        <v>2.68</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,234 +1605,234 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,234 +1859,234 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.4</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="n">
-        <v>3.9</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.36</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,261 +2096,769 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 14:46:33</t>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Icelandic Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>16:15:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KR Reykjavik</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-20 17:02:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-20 17:02:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Novorizontino</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>2026-06-20 14:46:33</t>
+      <c r="Q9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-20 17:02:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -878,7 +878,7 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
         <v>2.28</v>
@@ -890,7 +890,7 @@
         <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
         <v>1.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -1153,7 +1153,7 @@
         <v>3.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U3" t="n">
         <v>2.1</v>
@@ -1243,7 +1243,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1527,22 @@
         <v>13</v>
       </c>
       <c r="BH4" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.64</v>
+        <v>1.88</v>
       </c>
       <c r="BJ4" t="n">
         <v>13</v>
       </c>
       <c r="BK4" t="n">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="BN4" t="n">
         <v>8.800000000000001</v>
@@ -1554,13 +1554,13 @@
         <v>30</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="BR4" t="n">
         <v>46</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.76</v>
+        <v>1.81</v>
       </c>
       <c r="BT4" t="n">
         <v>8</v>
@@ -1572,23 +1572,23 @@
         <v>26</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.64</v>
+        <v>1.75</v>
       </c>
       <c r="BX4" t="n">
         <v>40</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.74</v>
+        <v>1.8</v>
       </c>
       <c r="BZ4" t="n">
         <v>30</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.68</v>
+        <v>1.77</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>
@@ -1649,22 +1649,22 @@
         <v>1.37</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="R5" t="n">
         <v>1.28</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T5" t="n">
         <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.49</v>
@@ -1730,7 +1730,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR5" t="n">
         <v>13</v>
@@ -1739,13 +1739,13 @@
         <v>3.95</v>
       </c>
       <c r="AT5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
         <v>3.9</v>
@@ -1754,10 +1754,10 @@
         <v>14</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="BA5" t="n">
         <v>34</v>
@@ -1790,13 +1790,13 @@
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN5" t="n">
         <v>6.2</v>
@@ -1808,31 +1808,31 @@
         <v>25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT5" t="n">
         <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -1891,13 +1891,13 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.69</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>1.39</v>
@@ -1915,10 +1915,10 @@
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
         <v>1.2</v>
@@ -1981,52 +1981,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -2038,55 +2038,55 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.04</v>
@@ -2166,13 +2166,13 @@
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
         <v>1.01</v>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2292,55 +2292,55 @@
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-20 17:02:19</t>
+          <t>2026-06-20 19:17:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -959,10 +959,10 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP2" t="n">
         <v>14.5</v>
@@ -974,7 +974,7 @@
         <v>19</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -986,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.36</v>
+        <v>2.86</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -998,25 +998,25 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.36</v>
+        <v>2.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.32</v>
+        <v>2.8</v>
       </c>
       <c r="BC2" t="n">
         <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.46</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.46</v>
+        <v>24</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
         <v>2.64</v>
@@ -1631,7 +1631,7 @@
         <v>3.05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
         <v>3.65</v>
@@ -1643,7 +1643,7 @@
         <v>1.08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
         <v>1.37</v>
@@ -1664,19 +1664,19 @@
         <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.49</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.52</v>
-      </c>
       <c r="X5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
@@ -1685,25 +1685,25 @@
         <v>55</v>
       </c>
       <c r="AB5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG5" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>23</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>22</v>
       </c>
       <c r="AI5" t="n">
         <v>60</v>
@@ -1712,7 +1712,7 @@
         <v>60</v>
       </c>
       <c r="AK5" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
         <v>60</v>
@@ -1724,61 +1724,61 @@
         <v>44</v>
       </c>
       <c r="AO5" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR5" t="n">
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.9</v>
+        <v>24</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.85</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="n">
         <v>3.25</v>
@@ -1802,7 +1802,7 @@
         <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BP5" t="n">
         <v>25</v>
@@ -1820,7 +1820,7 @@
         <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
         <v>4.7</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -2235,52 +2235,52 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J8" t="n">
         <v>2.9</v>
@@ -2399,212 +2399,212 @@
         <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q8" t="n">
         <v>2.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>
@@ -2635,230 +2635,230 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BV9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BX9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-20 19:17:09</t>
+          <t>2026-06-20 21:31:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -968,7 +968,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR2" t="n">
         <v>19</v>
@@ -980,10 +980,10 @@
         <v>9</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>2.44</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>2.64</v>
       </c>
       <c r="AW2" t="n">
         <v>2.86</v>
@@ -995,7 +995,7 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>13</v>
+        <v>2.66</v>
       </c>
       <c r="BA2" t="n">
         <v>2.88</v>
@@ -1013,7 +1013,7 @@
         <v>2.94</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>24</v>
@@ -1040,7 +1040,7 @@
         <v>7.4</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.95</v>
+        <v>1.49</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
@@ -1058,7 +1058,7 @@
         <v>10</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
         <v>38</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1386,22 +1386,22 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
         <v>3.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S4" t="n">
         <v>2.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1664,10 +1664,10 @@
         <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
         <v>1.49</v>
@@ -1802,7 +1802,7 @@
         <v>6.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="BP5" t="n">
         <v>25</v>
@@ -1820,7 +1820,7 @@
         <v>5.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -1873,220 +1873,220 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
         <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S6" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.99</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.04</v>
+        <v>1.63</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.83</v>
       </c>
       <c r="BN6" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="BT6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.13</v>
@@ -2411,7 +2411,7 @@
         <v>1.55</v>
       </c>
       <c r="P8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q8" t="n">
         <v>2.64</v>
@@ -2543,68 +2543,68 @@
         <v>6.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.05</v>
+        <v>2.72</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.5</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.5</v>
+        <v>9.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H9" t="n">
         <v>1.66</v>
@@ -2686,7 +2686,7 @@
         <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-20 21:31:28</t>
+          <t>2026-06-20 23:44:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB9"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,234 +843,234 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.25</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.66</v>
+        <v>1.06</v>
       </c>
       <c r="T2" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.92</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.64</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.86</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.66</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.94</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="n">
         <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="BN2" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="BR2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BT2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44:42</t>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>
@@ -1102,229 +1102,229 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I3" t="n">
         <v>4.1</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.4</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.37</v>
-      </c>
       <c r="S3" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="T3" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="X3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG3" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AL3" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>2.92</v>
       </c>
       <c r="AT3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.800000000000001</v>
+        <v>2.86</v>
       </c>
       <c r="AX3" t="n">
         <v>11</v>
       </c>
       <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BF3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>12</v>
-      </c>
       <c r="BG3" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>38</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BT3" t="n">
         <v>10</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
         <v>5.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BW3" t="n">
-        <v>10.5</v>
+        <v>1.81</v>
       </c>
       <c r="BX3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.5</v>
+        <v>1.83</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44:42</t>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.04</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N4" t="n">
         <v>3.85</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.96</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.5</v>
-      </c>
       <c r="X4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR4" t="n">
         <v>22</v>
       </c>
-      <c r="Y4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC4" t="n">
+      <c r="AS4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
       </c>
       <c r="AV4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
+      <c r="BF4" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>44</v>
+      </c>
+      <c r="BY4" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BZ4" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44:42</t>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
         <v>3.05</v>
       </c>
       <c r="H5" t="n">
-        <v>2.64</v>
+        <v>2.44</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.08</v>
+        <v>1.64</v>
       </c>
       <c r="R5" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.5</v>
       </c>
-      <c r="W5" t="n">
-        <v>1.49</v>
-      </c>
       <c r="X5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
         <v>22</v>
       </c>
       <c r="AA5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>55</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>60</v>
       </c>
       <c r="AK5" t="n">
         <v>38</v>
       </c>
       <c r="AL5" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM5" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.7</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.54</v>
+        <v>1.88</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>1.64</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.6</v>
+        <v>1.88</v>
       </c>
       <c r="BN5" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP5" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>1.77</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="BT5" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW5" t="n">
-        <v>7</v>
+        <v>1.75</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44:42</t>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>
@@ -1859,234 +1859,234 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>2.74</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T6" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AK6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF6" t="n">
         <v>24</v>
       </c>
-      <c r="AL6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="BG6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR6" t="n">
+      <c r="BN6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AS6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="BR6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS6" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AX6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.76</v>
-      </c>
       <c r="BT6" t="n">
-        <v>11</v>
+        <v>5.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.78</v>
+        <v>7.2</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,14 +2096,14 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44:42</t>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,234 +2113,234 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH7" t="n">
         <v>1000</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.04</v>
+        <v>1.62</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.82</v>
       </c>
       <c r="BN7" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="BP7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="BR7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.04</v>
+        <v>1.77</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.78</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44:42</t>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,498 +2367,752 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="P8" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>5.6</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.42</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK8" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN8" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO8" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP8" t="n">
         <v>1000</v>
       </c>
       <c r="BQ8" t="n">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-20 23:44:42</t>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Brazilian Serie C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Confianca</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-21 01:57:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Novorizontino</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="G10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="H10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="I10" t="n">
         <v>2.02</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" t="n">
         <v>3.15</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" t="n">
         <v>4.9</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
         <v>2.68</v>
       </c>
-      <c r="O9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="O10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.54</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" t="n">
         <v>2.06</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R10" t="n">
         <v>1.19</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S10" t="n">
         <v>3.7</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" t="n">
         <v>1.76</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>1.57</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V10" t="n">
         <v>1.98</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH9" t="n">
+      <c r="W10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH10" t="n">
         <v>3.6</v>
       </c>
-      <c r="BI9" t="n">
+      <c r="BI10" t="n">
         <v>2.42</v>
       </c>
-      <c r="BJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK9" t="n">
+      <c r="BJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM9" t="n">
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO9" t="n">
+      <c r="BN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BP9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ9" t="n">
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BR9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS9" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BT9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU9" t="n">
+      <c r="BT10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BV9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW9" t="n">
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
         <v>1.4</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA9" t="n">
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>1.4</v>
       </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>2026-06-20 23:44:42</t>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-21 01:57:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -860,16 +860,16 @@
         <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -1123,22 +1123,22 @@
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P3" t="n">
         <v>2.12</v>
@@ -1147,64 +1147,64 @@
         <v>1.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V3" t="n">
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="Z3" t="n">
         <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD3" t="n">
         <v>16</v>
       </c>
-      <c r="AC3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>21</v>
-      </c>
       <c r="AE3" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AI3" t="n">
         <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>44</v>
@@ -1213,118 +1213,118 @@
         <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AP3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11.5</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.92</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF3" t="n">
         <v>11</v>
       </c>
-      <c r="AW3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BF3" t="n">
+      <c r="BG3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG3" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.65</v>
+        <v>6.6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.89</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.74</v>
+        <v>6.4</v>
       </c>
       <c r="BR3" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.81</v>
+        <v>8</v>
       </c>
       <c r="BT3" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BU3" t="n">
         <v>5.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.81</v>
+        <v>8.4</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.83</v>
+        <v>9</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G4" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>4.7</v>
@@ -1380,67 +1380,67 @@
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA4" t="n">
         <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
         <v>12.5</v>
@@ -1455,16 +1455,16 @@
         <v>75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
         <v>15.5</v>
@@ -1476,13 +1476,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AT4" t="n">
         <v>8.4</v>
@@ -1491,46 +1491,46 @@
         <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ4" t="n">
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
@@ -1542,22 +1542,22 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN4" t="n">
         <v>4.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ4" t="n">
         <v>10</v>
       </c>
       <c r="BR4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS4" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
         <v>36</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BY4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -1622,13 +1622,13 @@
         <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="n">
         <v>2.44</v>
       </c>
       <c r="I5" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J5" t="n">
         <v>3.6</v>
@@ -1640,25 +1640,25 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="T5" t="n">
         <v>1.64</v>
@@ -1667,25 +1667,25 @@
         <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W5" t="n">
         <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
         <v>15.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
         <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
@@ -1703,7 +1703,7 @@
         <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
         <v>42</v>
@@ -1718,13 +1718,13 @@
         <v>46</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="n">
         <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
@@ -1736,7 +1736,7 @@
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1760,19 +1760,19 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
         <v>16.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J6" t="n">
         <v>3.25</v>
@@ -1891,7 +1891,7 @@
         <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1921,13 +1921,13 @@
         <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
@@ -1990,7 +1990,7 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
         <v>8.800000000000001</v>
@@ -2002,7 +2002,7 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
         <v>13.5</v>
@@ -2011,22 +2011,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC6" t="n">
         <v>6</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF6" t="n">
         <v>24</v>
@@ -2038,7 +2038,7 @@
         <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2050,10 +2050,10 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BO6" t="n">
         <v>4.4</v>
@@ -2074,10 +2074,10 @@
         <v>5.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BV6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
         <v>7.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G7" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
@@ -2145,31 +2145,31 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O7" t="n">
         <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q7" t="n">
         <v>2.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
         <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U7" t="n">
         <v>1.87</v>
@@ -2178,7 +2178,7 @@
         <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
@@ -2289,58 +2289,58 @@
         <v>8.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI7" t="n">
-        <v>1.82</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.62</v>
+        <v>8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.82</v>
+        <v>13</v>
       </c>
       <c r="BN7" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="BP7" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.66</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW7" t="n">
         <v>11</v>
       </c>
-      <c r="BU7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>1.77</v>
-      </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.78</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
         <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -2743,37 +2743,37 @@
         <v>48</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="AS9" t="n">
         <v>6.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AW9" t="n">
         <v>6.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>17.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>5.9</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>
@@ -2889,166 +2889,166 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="G10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="n">
         <v>3.6</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -881,7 +881,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
         <v>1.07</v>
@@ -893,10 +893,10 @@
         <v>1.07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -1114,16 +1114,16 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>4.1</v>
@@ -1135,7 +1135,7 @@
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.26</v>
@@ -1153,7 +1153,7 @@
         <v>2.92</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
         <v>2.26</v>
@@ -1162,22 +1162,22 @@
         <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
         <v>90</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>9</v>
@@ -1189,7 +1189,7 @@
         <v>44</v>
       </c>
       <c r="AF3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG3" t="n">
         <v>11</v>
@@ -1213,13 +1213,13 @@
         <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AP3" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ3" t="n">
         <v>14.5</v>
@@ -1228,10 +1228,10 @@
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.8</v>
@@ -1243,7 +1243,7 @@
         <v>28</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY3" t="n">
         <v>9.4</v>
@@ -1258,28 +1258,28 @@
         <v>21</v>
       </c>
       <c r="BC3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD3" t="n">
         <v>25</v>
       </c>
       <c r="BE3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF3" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF3" t="n">
-        <v>11</v>
-      </c>
       <c r="BG3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BI3" t="n">
         <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK3" t="n">
         <v>6.6</v>
@@ -1288,25 +1288,25 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BN3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BO3" t="n">
         <v>4.4</v>
       </c>
       <c r="BP3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR3" t="n">
         <v>26</v>
       </c>
       <c r="BS3" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BT3" t="n">
         <v>7.4</v>
@@ -1315,16 +1315,16 @@
         <v>5.3</v>
       </c>
       <c r="BV3" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BW3" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BX3" t="n">
         <v>38</v>
       </c>
       <c r="BY3" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
         <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1392,19 +1392,19 @@
         <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.78</v>
@@ -1413,34 +1413,34 @@
         <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W4" t="n">
         <v>2</v>
       </c>
       <c r="X4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y4" t="n">
         <v>16</v>
       </c>
-      <c r="Y4" t="n">
-        <v>17</v>
-      </c>
       <c r="Z4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
         <v>110</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AF4" t="n">
         <v>12.5</v>
@@ -1476,13 +1476,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
         <v>8.4</v>
@@ -1494,10 +1494,10 @@
         <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>9</v>
@@ -1506,37 +1506,37 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
         <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BF4" t="n">
         <v>11</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>8.4</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1548,7 +1548,7 @@
         <v>4.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP4" t="n">
         <v>13.5</v>
@@ -1557,7 +1557,7 @@
         <v>10</v>
       </c>
       <c r="BR4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BS4" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="n">
         <v>2.44</v>
@@ -1673,7 +1673,7 @@
         <v>1.5</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
         <v>15.5</v>
@@ -1718,25 +1718,25 @@
         <v>46</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN5" t="n">
         <v>28</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP5" t="n">
         <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AR5" t="n">
         <v>13</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW5" t="n">
         <v>18.5</v>
@@ -1760,25 +1760,25 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE5" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
         <v>16.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1876,22 @@
         <v>2.74</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1921,43 +1921,43 @@
         <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
         <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB6" t="n">
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
         <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
         <v>50</v>
@@ -1966,10 +1966,10 @@
         <v>50</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM6" t="n">
         <v>140</v>
@@ -1981,64 +1981,64 @@
         <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
         <v>8.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="AX6" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE6" t="n">
         <v>5.6</v>
       </c>
-      <c r="BA6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>7</v>
-      </c>
       <c r="BF6" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="BG6" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="n">
         <v>3.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ6" t="n">
         <v>10.5</v>
@@ -2050,10 +2050,10 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO6" t="n">
         <v>4.4</v>
@@ -2074,10 +2074,10 @@
         <v>5.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="BV6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW6" t="n">
         <v>7.2</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -2127,193 +2127,193 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="G7" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
         <v>1.87</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA7" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AE7" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
         <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AK7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
         <v>180</v>
       </c>
       <c r="AN7" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="AS7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX7" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>3.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BD7" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
         <v>11</v>
       </c>
       <c r="BK7" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ7" t="n">
         <v>7.2</v>
@@ -2325,22 +2325,22 @@
         <v>10</v>
       </c>
       <c r="BT7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU7" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
         <v>1.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -2653,10 +2653,10 @@
         <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
         <v>2.52</v>
@@ -2665,7 +2665,7 @@
         <v>1.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
         <v>2.62</v>
@@ -2674,7 +2674,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.1</v>
@@ -2689,10 +2689,10 @@
         <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z9" t="n">
         <v>15</v>
@@ -2701,7 +2701,7 @@
         <v>46</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
         <v>7.4</v>
@@ -2743,64 +2743,64 @@
         <v>48</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.85</v>
+        <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB9" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BC9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD9" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE9" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="n">
         <v>2.72</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="BJ9" t="n">
         <v>11.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>
@@ -2895,16 +2895,16 @@
         <v>6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="I10" t="n">
         <v>1.87</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2931,7 +2931,7 @@
         <v>4.3</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
         <v>1.79</v>
@@ -2958,13 +2958,13 @@
         <v>16.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>11</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF10" t="n">
         <v>48</v>
@@ -2976,10 +2976,10 @@
         <v>26</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AK10" t="n">
         <v>120</v>
@@ -2988,13 +2988,13 @@
         <v>130</v>
       </c>
       <c r="AM10" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN10" t="n">
         <v>190</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP10" t="n">
         <v>9.199999999999999</v>
@@ -3021,7 +3021,7 @@
         <v>19</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AY10" t="n">
         <v>19.5</v>
@@ -3033,19 +3033,19 @@
         <v>7.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE10" t="n">
         <v>8</v>
       </c>
-      <c r="BD10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BF10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG10" t="n">
         <v>12</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Latvian Virsliga</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -848,55 +848,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Rigas Futbola Skola</t>
+          <t>Dila Gori</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FC Rustavi</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G2" t="n">
+        <v>110</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I2" t="n">
+        <v>110</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K2" t="n">
+        <v>950</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
         <v>1.07</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="H2" t="n">
-        <v>16</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1.26</v>
-      </c>
       <c r="O2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.07</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.07</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.24</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -908,7 +908,7 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -1073,21 +1073,21 @@
         <v>1.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Latvian Virsliga</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,234 +1097,234 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Rigas Futbola Skola</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="H3" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>1.26</v>
       </c>
       <c r="O3" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.76</v>
+        <v>1.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>2.92</v>
+        <v>1.07</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>2.26</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
@@ -1356,229 +1356,229 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I4" t="n">
         <v>4.2</v>
       </c>
-      <c r="I4" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD4" t="n">
         <v>16</v>
       </c>
-      <c r="Z4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY4" t="n">
         <v>9.4</v>
       </c>
-      <c r="AC4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD4" t="n">
+      <c r="AZ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AE4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="BD4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ4" t="n">
+      <c r="BG4" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP4" t="n">
         <v>14</v>
       </c>
-      <c r="AR4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW4" t="n">
+      <c r="BQ4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW4" t="n">
         <v>10</v>
       </c>
-      <c r="AX4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA4" t="n">
+      <c r="BX4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY4" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
@@ -1605,251 +1605,251 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>1.91</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.64</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z5" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>16</v>
       </c>
       <c r="AH5" t="n">
         <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="AJ5" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>15.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>8.800000000000001</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY5" t="n">
         <v>11.5</v>
       </c>
-      <c r="BA5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>13</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>30</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.8</v>
-      </c>
       <c r="BZ5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,244 +1859,244 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="I6" t="n">
-        <v>2.94</v>
+        <v>2.64</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.45</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.28</v>
-      </c>
       <c r="S6" t="n">
-        <v>3.85</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="V6" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="W6" t="n">
         <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI6" t="n">
         <v>42</v>
       </c>
-      <c r="AF6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>50</v>
-      </c>
       <c r="AJ6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
         <v>38</v>
       </c>
       <c r="AL6" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AP6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT6" t="n">
         <v>10</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AX6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AY6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>5</v>
-      </c>
       <c r="BH6" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.52</v>
+        <v>1.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.2</v>
+        <v>1.64</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.800000000000001</v>
+        <v>1.88</v>
       </c>
       <c r="BN6" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.4</v>
+        <v>1.77</v>
       </c>
       <c r="BR6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.81</v>
       </c>
       <c r="BT6" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BW6" t="n">
-        <v>7.2</v>
+        <v>1.75</v>
       </c>
       <c r="BX6" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
@@ -2113,234 +2113,234 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.82</v>
+        <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
-        <v>5.9</v>
+        <v>2.94</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
         <v>9</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="BN7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP7" t="n">
         <v>25</v>
       </c>
-      <c r="AE7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="BQ7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ7" t="n">
+      <c r="BV7" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW7" t="n">
         <v>7.2</v>
       </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,234 +2367,234 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>1.07</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT8" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV8" t="n">
         <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,251 +2621,251 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>2.52</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="BJ9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
         <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.9</v>
+        <v>1.04</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,244 +2875,498 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confianca</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5.5</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.76</v>
+        <v>2.62</v>
       </c>
       <c r="I10" t="n">
-        <v>1.87</v>
+        <v>2.78</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="T10" t="n">
         <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>2.14</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF10" t="n">
         <v>21</v>
       </c>
-      <c r="AB10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AG10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV10" t="n">
         <v>11</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AW10" t="n">
         <v>24</v>
       </c>
-      <c r="AF10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>210</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>19</v>
-      </c>
       <c r="AX10" t="n">
-        <v>7.2</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
-        <v>19.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC10" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>7.8</v>
       </c>
       <c r="BD10" t="n">
         <v>7.8</v>
       </c>
       <c r="BE10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-21 08:35:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB11" t="n">
         <v>8</v>
       </c>
-      <c r="BF10" t="n">
+      <c r="BC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE11" t="n">
         <v>8</v>
       </c>
-      <c r="BG10" t="n">
+      <c r="BF11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG11" t="n">
         <v>12</v>
       </c>
-      <c r="BH10" t="n">
+      <c r="BH11" t="n">
         <v>3.6</v>
       </c>
-      <c r="BI10" t="n">
+      <c r="BI11" t="n">
         <v>2.42</v>
       </c>
-      <c r="BJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK10" t="n">
+      <c r="BJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO10" t="n">
+      <c r="BN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BP10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ10" t="n">
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BT10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU10" t="n">
+      <c r="BT11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BX10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY10" t="n">
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>1.4</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
         <v>1.4</v>
       </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-21 06:22:58</t>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
-        <v>110</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.07</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BN2" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1135,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P3" t="n">
         <v>1.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -1371,16 +1371,16 @@
         <v>2.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
         <v>4.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1419,7 +1419,7 @@
         <v>1.92</v>
       </c>
       <c r="X4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
         <v>17</v>
@@ -1434,7 +1434,7 @@
         <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>16</v>
@@ -1449,7 +1449,7 @@
         <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI4" t="n">
         <v>60</v>
@@ -1482,7 +1482,7 @@
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
@@ -1518,19 +1518,19 @@
         <v>25</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.8</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.199999999999999</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="I6" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="K6" t="n">
         <v>3.85</v>
@@ -1897,34 +1897,34 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
         <v>1.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -2011,7 +2011,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
         <v>3.95</v>
@@ -2038,65 +2038,65 @@
         <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.88</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="BR6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.81</v>
+        <v>1.04</v>
       </c>
       <c r="BT6" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.77</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -2130,10 +2130,10 @@
         <v>2.74</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
         <v>2.94</v>
@@ -2142,7 +2142,7 @@
         <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.38</v>
@@ -2166,7 +2166,7 @@
         <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T7" t="n">
         <v>1.84</v>
@@ -2178,7 +2178,7 @@
         <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>1.82</v>
       </c>
       <c r="G8" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H8" t="n">
         <v>4.9</v>
@@ -2396,7 +2396,7 @@
         <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
         <v>1.46</v>
@@ -2408,7 +2408,7 @@
         <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
         <v>1.74</v>
@@ -2429,7 +2429,7 @@
         <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
         <v>2.06</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
         <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="I10" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="J10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K10" t="n">
         <v>3.3</v>
@@ -2910,25 +2910,25 @@
         <v>1.58</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N10" t="n">
         <v>2.5</v>
       </c>
       <c r="O10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.54</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
         <v>2.62</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T10" t="n">
         <v>2.08</v>
@@ -2937,118 +2937,118 @@
         <v>1.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
         <v>10</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>7.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK10" t="n">
         <v>55</v>
       </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ10" t="n">
+      <c r="AL10" t="n">
         <v>90</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AM10" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO10" t="n">
         <v>80</v>
       </c>
-      <c r="AL10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>60</v>
-      </c>
       <c r="AP10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS10" t="n">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW10" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>28</v>
+        <v>6.2</v>
       </c>
       <c r="BH10" t="n">
         <v>2.72</v>
@@ -3066,53 +3066,53 @@
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ10" t="n">
         <v>1000</v>
       </c>
       <c r="CA10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G11" t="n">
         <v>6.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I11" t="n">
         <v>1.87</v>
@@ -3158,13 +3158,13 @@
         <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N11" t="n">
         <v>2.96</v>
@@ -3194,7 +3194,7 @@
         <v>2.14</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB11"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,13 +896,13 @@
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
@@ -953,7 +953,7 @@
         <v>38</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>160</v>
@@ -968,16 +968,16 @@
         <v>4.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
         <v>6</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
         <v>3.55</v>
@@ -986,7 +986,7 @@
         <v>4.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
         <v>4.6</v>
@@ -1004,7 +1004,7 @@
         <v>5.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD2" t="n">
         <v>5.9</v>
@@ -1061,10 +1061,10 @@
         <v>4.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.800000000000001</v>
+        <v>2.3</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
@@ -1111,172 +1111,172 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="G3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.94</v>
       </c>
-      <c r="H3" t="n">
-        <v>16</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1291,16 +1291,16 @@
         <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
@@ -1334,14 +1334,14 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swedish Superettan</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1356,239 +1356,239 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ljungskile</t>
+          <t>FC Spaeri</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.99</v>
+        <v>1.48</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.92</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
         <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>28</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BR4" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BT4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
@@ -1610,229 +1610,229 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Varbergs BoIS</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ljungskile</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA5" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH5" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="AX5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF5" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>11</v>
       </c>
       <c r="BG5" t="n">
         <v>10.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP5" t="n">
         <v>14</v>
       </c>
-      <c r="BN5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BQ5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW5" t="n">
         <v>10</v>
       </c>
-      <c r="BR5" t="n">
-        <v>28</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>36</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>11</v>
-      </c>
       <c r="BX5" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:05:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Orebro</t>
+          <t>Varbergs BoIS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sandvikens IF</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.66</v>
+        <v>1.94</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.74</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.85</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.75</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
         <v>1.98</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH6" t="n">
         <v>21</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AI6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX6" t="n">
         <v>44</v>
       </c>
-      <c r="AB6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>1000</v>
-      </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Swedish Superettan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>14:05:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Orebro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Sandvikens IF</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="G7" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>1.75</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>3.95</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Z7" t="n">
         <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI7" t="n">
         <v>42</v>
       </c>
-      <c r="AF7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>50</v>
-      </c>
       <c r="AJ7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK7" t="n">
         <v>38</v>
       </c>
       <c r="AL7" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM7" t="n">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AO7" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
         <v>10</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AU7" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="AX7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>15.5</v>
       </c>
-      <c r="AY7" t="n">
+      <c r="BH7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>5</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ7" t="n">
+      <c r="BT7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY7" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
@@ -2367,234 +2367,234 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.82</v>
+        <v>2.74</v>
       </c>
       <c r="G8" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>4.9</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>2.94</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
         <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
         <v>9</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AD8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="BN8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP8" t="n">
         <v>25</v>
       </c>
-      <c r="AE8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU8" t="n">
+      <c r="BQ8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>24</v>
+      </c>
+      <c r="BW8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Icelandic Urvalsdeild</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,234 +2621,234 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KR Reykjavik</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IA Akranes</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie C</t>
+          <t>Icelandic Urvalsdeild</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2875,251 +2875,251 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Confianca</t>
+          <t>KR Reykjavik</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>IA Akranes</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>5.5</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.24</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN10" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP10" t="n">
         <v>1000</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR10" t="n">
         <v>1000</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BU10" t="n">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BV10" t="n">
         <v>1000</v>
       </c>
       <c r="BW10" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX10" t="n">
         <v>1000</v>
       </c>
       <c r="BY10" t="n">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 10:48:08</t>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie C</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3129,244 +3129,498 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Confianca</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.4</v>
+        <v>2.88</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>1.77</v>
+        <v>2.68</v>
       </c>
       <c r="I11" t="n">
-        <v>1.87</v>
+        <v>2.98</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="T11" t="n">
         <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>2.14</v>
+        <v>1.51</v>
       </c>
       <c r="W11" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="X11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB11" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>16.5</v>
       </c>
       <c r="AC11" t="n">
         <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>10</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA12" t="n">
         <v>24</v>
       </c>
-      <c r="AF11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI11" t="n">
+      <c r="AB12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI12" t="n">
         <v>60</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AJ12" t="n">
         <v>210</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AK12" t="n">
         <v>120</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AL12" t="n">
         <v>130</v>
       </c>
-      <c r="AM11" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN11" t="n">
+      <c r="AM12" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN12" t="n">
         <v>190</v>
       </c>
-      <c r="AO11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="AO12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AQ12" t="n">
         <v>6</v>
       </c>
-      <c r="AR11" t="n">
+      <c r="AR12" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS11" t="n">
+      <c r="AS12" t="n">
         <v>16.5</v>
       </c>
-      <c r="AT11" t="n">
+      <c r="AT12" t="n">
         <v>13</v>
       </c>
-      <c r="AU11" t="n">
+      <c r="AU12" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AV12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW11" t="n">
+      <c r="AW12" t="n">
         <v>19</v>
       </c>
-      <c r="AX11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AZ11" t="n">
+      <c r="AX12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>21</v>
       </c>
-      <c r="BA11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB11" t="n">
+      <c r="BA12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>60</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BY12" t="n">
         <v>8</v>
       </c>
-      <c r="BC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE11" t="n">
+      <c r="BZ12" t="n">
+        <v>34</v>
+      </c>
+      <c r="CA12" t="n">
         <v>8</v>
       </c>
-      <c r="BF11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>2026-06-21 10:48:08</t>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -887,19 +887,19 @@
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
         <v>1.93</v>
@@ -917,7 +917,7 @@
         <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
         <v>80</v>
@@ -926,7 +926,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>15.5</v>
@@ -962,61 +962,61 @@
         <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AR2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB2" t="n">
         <v>6</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BC2" t="n">
         <v>6</v>
       </c>
-      <c r="BB2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
         <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
         <v>1.14</v>
@@ -1144,19 +1144,19 @@
         <v>4.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R3" t="n">
         <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="T3" t="n">
         <v>2.36</v>
       </c>
       <c r="U3" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
@@ -1192,7 +1192,7 @@
         <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>80</v>
@@ -1204,7 +1204,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
@@ -1219,16 +1219,16 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AT3" t="n">
         <v>1.76</v>
@@ -1240,7 +1240,7 @@
         <v>1.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
         <v>5.4</v>
@@ -1252,7 +1252,7 @@
         <v>1.88</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BB3" t="n">
         <v>4.7</v>
@@ -1270,7 +1270,7 @@
         <v>1.94</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BH3" t="n">
         <v>1000</v>
@@ -1282,13 +1282,13 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BN3" t="n">
         <v>4.3</v>
@@ -1306,25 +1306,25 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1389,16 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R4" t="n">
         <v>1.45</v>
@@ -1431,10 +1431,10 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
         <v>28</v>
@@ -1443,10 +1443,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>24</v>
@@ -1455,10 +1455,10 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AL4" t="n">
         <v>36</v>
@@ -1467,64 +1467,64 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.79</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1622,10 +1622,10 @@
         <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I5" t="n">
         <v>4.1</v>
@@ -1634,7 +1634,7 @@
         <v>3.55</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.29</v>
@@ -1643,19 +1643,19 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
         <v>2.94</v>
@@ -1664,13 +1664,13 @@
         <v>1.67</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1679,7 +1679,7 @@
         <v>16.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
         <v>90</v>
@@ -1688,7 +1688,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1715,7 +1715,7 @@
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
         <v>100</v>
@@ -1724,22 +1724,22 @@
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>15</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AR5" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
@@ -1748,19 +1748,19 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB5" t="n">
         <v>21</v>
@@ -1769,16 +1769,16 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE5" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1873,76 +1873,76 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
         <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
         <v>20</v>
@@ -1951,13 +1951,13 @@
         <v>65</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
         <v>70</v>
@@ -1966,16 +1966,16 @@
         <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO6" t="n">
         <v>70</v>
@@ -1987,10 +1987,10 @@
         <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -2002,7 +2002,7 @@
         <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2011,10 +2011,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.8</v>
+        <v>44</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -2023,16 +2023,16 @@
         <v>18</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH6" t="n">
         <v>3.5</v>
@@ -2050,7 +2050,7 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2059,7 +2059,7 @@
         <v>4.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ6" t="n">
         <v>7.4</v>
@@ -2071,7 +2071,7 @@
         <v>10</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU6" t="n">
         <v>5.7</v>
@@ -2086,7 +2086,7 @@
         <v>44</v>
       </c>
       <c r="BY6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="I7" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
         <v>3.8</v>
@@ -2172,13 +2172,13 @@
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>22</v>
@@ -2196,7 +2196,7 @@
         <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD7" t="n">
         <v>14.5</v>
@@ -2235,7 +2235,7 @@
         <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
@@ -2262,22 +2262,22 @@
         <v>18.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BB7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE7" t="n">
         <v>4.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
         <v>2.98</v>
@@ -2411,7 +2411,7 @@
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
         <v>2.12</v>
@@ -2426,13 +2426,13 @@
         <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
         <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
         <v>14.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I9" t="n">
         <v>5.5</v>
@@ -2650,10 +2650,10 @@
         <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2668,7 +2668,7 @@
         <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R9" t="n">
         <v>1.31</v>
@@ -2680,7 +2680,7 @@
         <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
@@ -2692,7 +2692,7 @@
         <v>15.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
         <v>50</v>
@@ -2701,10 +2701,10 @@
         <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD9" t="n">
         <v>25</v>
@@ -2722,7 +2722,7 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
         <v>25</v>
@@ -2737,7 +2737,7 @@
         <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>120</v>
@@ -2746,13 +2746,13 @@
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2761,10 +2761,10 @@
         <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX9" t="n">
         <v>9.800000000000001</v>
@@ -2773,28 +2773,28 @@
         <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="BA9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD9" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH9" t="n">
         <v>3.2</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
         <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.76</v>
+        <v>1.02</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -3143,25 +3143,25 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I11" t="n">
         <v>2.88</v>
       </c>
-      <c r="G11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.98</v>
-      </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="M11" t="n">
         <v>1.12</v>
@@ -3173,13 +3173,13 @@
         <v>1.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
         <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
         <v>5.5</v>
@@ -3191,10 +3191,10 @@
         <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
         <v>10.5</v>
@@ -3215,7 +3215,7 @@
         <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -3233,7 +3233,7 @@
         <v>90</v>
       </c>
       <c r="AJ11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK11" t="n">
         <v>60</v>
@@ -3242,7 +3242,7 @@
         <v>90</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AN11" t="n">
         <v>75</v>
@@ -3251,7 +3251,7 @@
         <v>65</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.2</v>
@@ -3260,10 +3260,10 @@
         <v>12.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
         <v>5.4</v>
@@ -3272,7 +3272,7 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AX11" t="n">
         <v>14</v>
@@ -3284,89 +3284,89 @@
         <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BH11" t="n">
         <v>2.72</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BN11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -3400,13 +3400,13 @@
         <v>5.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="I12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -3415,58 +3415,58 @@
         <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="O12" t="n">
         <v>1.43</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
         <v>24</v>
       </c>
       <c r="AB12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>12.5</v>
@@ -3502,7 +3502,7 @@
         <v>190</v>
       </c>
       <c r="AO12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP12" t="n">
         <v>9.199999999999999</v>
@@ -3529,7 +3529,7 @@
         <v>19</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AY12" t="n">
         <v>19</v>
@@ -3538,22 +3538,22 @@
         <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
@@ -3562,7 +3562,7 @@
         <v>3.1</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
@@ -3583,7 +3583,7 @@
         <v>4.9</v>
       </c>
       <c r="BP12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
         <v>8.800000000000001</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -887,7 +887,7 @@
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q2" t="n">
         <v>2.2</v>
@@ -950,7 +950,7 @@
         <v>38</v>
       </c>
       <c r="AK2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -965,31 +965,31 @@
         <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
         <v>5.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AY2" t="n">
         <v>4.6</v>
@@ -1001,7 +1001,7 @@
         <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC2" t="n">
         <v>6</v>
@@ -1016,7 +1016,7 @@
         <v>6</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1114,22 +1114,22 @@
         <v>1.08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H3" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I3" t="n">
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
         <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
@@ -1141,16 +1141,16 @@
         <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q3" t="n">
         <v>1.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T3" t="n">
         <v>2.36</v>
@@ -1162,7 +1162,7 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="X3" t="n">
         <v>75</v>
@@ -1273,10 +1273,10 @@
         <v>1.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
@@ -1649,7 +1649,7 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
         <v>1.78</v>
@@ -1661,10 +1661,10 @@
         <v>2.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
@@ -1724,7 +1724,7 @@
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
@@ -1784,7 +1784,7 @@
         <v>3.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
@@ -1808,7 +1808,7 @@
         <v>14</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BR5" t="n">
         <v>26</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1906,7 @@
         <v>1.96</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G7" t="n">
         <v>2.98</v>
@@ -2163,7 +2163,7 @@
         <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S7" t="n">
         <v>2.92</v>
@@ -2181,7 +2181,7 @@
         <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
         <v>15.5</v>
@@ -2244,10 +2244,10 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU7" t="n">
         <v>7.6</v>
@@ -2268,10 +2268,10 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
@@ -2280,7 +2280,7 @@
         <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF7" t="n">
         <v>16.5</v>
@@ -2298,7 +2298,7 @@
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -2384,16 +2384,16 @@
         <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
         <v>2.72</v>
       </c>
       <c r="I8" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.55</v>
@@ -2411,7 +2411,7 @@
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
         <v>2.12</v>
@@ -2432,7 +2432,7 @@
         <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
         <v>14.5</v>
@@ -2456,13 +2456,13 @@
         <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
@@ -2498,7 +2498,7 @@
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
@@ -2519,34 +2519,34 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BC8" t="n">
         <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="n">
         <v>3.25</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ8" t="n">
         <v>10.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
         <v>1.92</v>
@@ -2644,13 +2644,13 @@
         <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.38</v>
@@ -2659,37 +2659,37 @@
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
         <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
         <v>2.08</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y9" t="n">
         <v>19</v>
@@ -2719,13 +2719,13 @@
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK9" t="n">
         <v>26</v>
@@ -2737,7 +2737,7 @@
         <v>150</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO9" t="n">
         <v>120</v>
@@ -2746,13 +2746,13 @@
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
@@ -2761,10 +2761,10 @@
         <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
         <v>9.800000000000001</v>
@@ -2773,46 +2773,46 @@
         <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
@@ -2821,10 +2821,10 @@
         <v>3.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2836,19 +2836,19 @@
         <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,13 +2913,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.1</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
         <v>1.01</v>
@@ -2928,13 +2928,13 @@
         <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.02</v>
+        <v>1.78</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2943,166 +2943,166 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BN10" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BP10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.04</v>
+        <v>1.95</v>
       </c>
       <c r="BR10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS10" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="BT10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="BV10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -3146,13 +3146,13 @@
         <v>3.05</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
         <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J11" t="n">
         <v>2.92</v>
@@ -3194,7 +3194,7 @@
         <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X11" t="n">
         <v>10.5</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -3403,10 +3403,10 @@
         <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -3445,7 +3445,7 @@
         <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
@@ -3484,7 +3484,7 @@
         <v>30</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
         <v>210</v>
@@ -3541,19 +3541,19 @@
         <v>5.4</v>
       </c>
       <c r="BB12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC12" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC12" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
@@ -3568,7 +3568,7 @@
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -863,13 +863,13 @@
         <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I2" t="n">
         <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
@@ -881,37 +881,37 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q2" t="n">
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
         <v>11.5</v>
@@ -920,16 +920,16 @@
         <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
         <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE2" t="n">
         <v>60</v>
@@ -938,16 +938,16 @@
         <v>15.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
@@ -956,67 +956,67 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN2" t="n">
         <v>34</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="J3" t="n">
         <v>14</v>
@@ -1129,19 +1129,19 @@
         <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
         <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Q3" t="n">
         <v>1.25</v>
@@ -1165,10 +1165,10 @@
         <v>10</v>
       </c>
       <c r="X3" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,10 +1177,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AD3" t="n">
         <v>160</v>
@@ -1195,7 +1195,7 @@
         <v>970</v>
       </c>
       <c r="AH3" t="n">
-        <v>80</v>
+        <v>330</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1204,91 +1204,91 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>330</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.91</v>
+        <v>7.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.75</v>
+        <v>7.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.76</v>
+        <v>9</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.84</v>
+        <v>8.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.9</v>
+        <v>7.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.75</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.91</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="BC3" t="n">
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.1</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.91</v>
+        <v>10</v>
       </c>
       <c r="BF3" t="n">
         <v>1.94</v>
       </c>
       <c r="BG3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>1.75</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>970</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.76</v>
       </c>
       <c r="BN3" t="n">
         <v>4.3</v>
@@ -1306,25 +1306,25 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>2.76</v>
+        <v>1.75</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="G4" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" t="n">
         <v>5.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>6.2</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1389,7 +1389,7 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
@@ -1401,130 +1401,130 @@
         <v>1.66</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
         <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
         <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="Y4" t="n">
-        <v>27</v>
+        <v>130</v>
       </c>
       <c r="Z4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>180</v>
       </c>
       <c r="AK4" t="n">
         <v>970</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4.6</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AW4" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="AX4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BF4" t="n">
         <v>3.8</v>
       </c>
-      <c r="AY4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BG4" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1.83</v>
       </c>
       <c r="BH4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
         <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.29</v>
@@ -1649,7 +1649,7 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
         <v>1.78</v>
@@ -1667,16 +1667,16 @@
         <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
         <v>36</v>
@@ -1700,7 +1700,7 @@
         <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
         <v>16</v>
@@ -1718,7 +1718,7 @@
         <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN5" t="n">
         <v>13</v>
@@ -1736,10 +1736,10 @@
         <v>19.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>7.6</v>
@@ -1754,7 +1754,7 @@
         <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>14</v>
@@ -1769,13 +1769,13 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
         <v>23</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
@@ -1811,10 +1811,10 @@
         <v>10</v>
       </c>
       <c r="BR5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>7.4</v>
@@ -1832,7 +1832,7 @@
         <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>1.98</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
         <v>4.2</v>
@@ -1924,7 +1924,7 @@
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1972,7 +1972,7 @@
         <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="AN6" t="n">
         <v>15.5</v>
@@ -1987,10 +1987,10 @@
         <v>14</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -2032,7 +2032,7 @@
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="n">
         <v>3.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="G7" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H7" t="n">
         <v>2.52</v>
       </c>
       <c r="I7" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
@@ -2175,10 +2175,10 @@
         <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
         <v>21</v>
@@ -2244,7 +2244,7 @@
         <v>13</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="AT7" t="n">
         <v>10.5</v>
@@ -2268,7 +2268,7 @@
         <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BB7" t="n">
         <v>4.2</v>
@@ -2277,7 +2277,7 @@
         <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="BE7" t="n">
         <v>4.3</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
         <v>2.72</v>
@@ -2420,31 +2420,31 @@
         <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
         <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
         <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AA8" t="n">
-        <v>46</v>
+        <v>220</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
@@ -2456,7 +2456,7 @@
         <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AF8" t="n">
         <v>22</v>
@@ -2468,10 +2468,10 @@
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AK8" t="n">
         <v>38</v>
@@ -2480,13 +2480,13 @@
         <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AO8" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AP8" t="n">
         <v>10</v>
@@ -2498,7 +2498,7 @@
         <v>15</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.7</v>
+        <v>36</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
@@ -2510,7 +2510,7 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2519,28 +2519,28 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.7</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BC8" t="n">
         <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.8</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG8" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.4</v>
       </c>
       <c r="BH8" t="n">
         <v>3.25</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
         <v>1.92</v>
@@ -2644,22 +2644,22 @@
         <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
@@ -2689,7 +2689,7 @@
         <v>2.08</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y9" t="n">
         <v>19</v>
@@ -2698,7 +2698,7 @@
         <v>50</v>
       </c>
       <c r="AA9" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>9.4</v>
@@ -2710,7 +2710,7 @@
         <v>25</v>
       </c>
       <c r="AE9" t="n">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AF9" t="n">
         <v>13.5</v>
@@ -2722,7 +2722,7 @@
         <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
         <v>24</v>
@@ -2731,40 +2731,40 @@
         <v>26</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>17.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AP9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.85</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
         <v>9.800000000000001</v>
@@ -2773,28 +2773,28 @@
         <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
         <v>11.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH9" t="n">
         <v>3.15</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K10" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,28 +2913,28 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R10" t="n">
         <v>2.16</v>
       </c>
       <c r="S10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="T10" t="n">
         <v>1.4</v>
       </c>
       <c r="U10" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2943,16 +2943,16 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>950</v>
+        <v>130</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>100</v>
       </c>
       <c r="Z10" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB10" t="n">
         <v>22</v>
@@ -2961,13 +2961,13 @@
         <v>17</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AG10" t="n">
         <v>15.5</v>
@@ -2976,7 +2976,7 @@
         <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
         <v>24</v>
@@ -2988,67 +2988,67 @@
         <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AN10" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
         <v>22</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.9</v>
+        <v>32</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.85</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
         <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD10" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BE10" t="n">
         <v>26</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BH10" t="n">
         <v>1000</v>
@@ -3060,7 +3060,7 @@
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>1.92</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -3143,40 +3143,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="I11" t="n">
-        <v>2.86</v>
+        <v>2.26</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M11" t="n">
         <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O11" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="P11" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
         <v>1.19</v>
@@ -3185,94 +3185,94 @@
         <v>5.5</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="X11" t="n">
         <v>10.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="Z11" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
         <v>65</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
         <v>8.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AG11" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AH11" t="n">
         <v>29</v>
       </c>
       <c r="AI11" t="n">
-        <v>90</v>
+        <v>460</v>
       </c>
       <c r="AJ11" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>230</v>
+        <v>500</v>
       </c>
       <c r="AN11" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AO11" t="n">
         <v>65</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>5.4</v>
       </c>
       <c r="AV11" t="n">
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
         <v>14</v>
@@ -3284,89 +3284,89 @@
         <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN11" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO11" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>18</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BT11" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>5.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
         <v>1.77</v>
@@ -3421,10 +3421,10 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P12" t="n">
         <v>1.65</v>
@@ -3436,10 +3436,10 @@
         <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
         <v>1.78</v>
@@ -3481,7 +3481,7 @@
         <v>28</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
@@ -3529,7 +3529,7 @@
         <v>19</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY12" t="n">
         <v>19</v>
@@ -3538,22 +3538,22 @@
         <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC12" t="n">
         <v>5.8</v>
       </c>
-      <c r="BC12" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BD12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
@@ -3568,7 +3568,7 @@
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
@@ -3598,13 +3598,13 @@
         <v>4.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="BV12" t="n">
         <v>14</v>
       </c>
       <c r="BW12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BX12" t="n">
         <v>36</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -893,10 +893,10 @@
         <v>2.2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="T2" t="n">
         <v>1.89</v>
@@ -908,7 +908,7 @@
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -983,19 +983,19 @@
         <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA2" t="n">
         <v>8.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L3" t="n">
         <v>1.19</v>
@@ -1135,40 +1135,40 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q3" t="n">
         <v>1.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="T3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
         <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="X3" t="n">
         <v>320</v>
       </c>
       <c r="Y3" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,19 +1177,19 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AC3" t="n">
         <v>80</v>
       </c>
       <c r="AD3" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>970</v>
@@ -1213,34 +1213,34 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT3" t="n">
         <v>9</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
@@ -1249,10 +1249,10 @@
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB3" t="n">
         <v>7.4</v>
@@ -1261,10 +1261,10 @@
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF3" t="n">
         <v>1.94</v>
@@ -1273,25 +1273,25 @@
         <v>10.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BI3" t="n">
         <v>5.3</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO3" t="n">
         <v>3.6</v>
@@ -1306,25 +1306,25 @@
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU3" t="n">
         <v>7.2</v>
       </c>
-      <c r="BT3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="H4" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1389,7 +1389,7 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.23</v>
@@ -1398,7 +1398,7 @@
         <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R4" t="n">
         <v>1.46</v>
@@ -1407,16 +1407,16 @@
         <v>2.68</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
         <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W4" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="X4" t="n">
         <v>90</v>
@@ -1425,13 +1425,13 @@
         <v>130</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
         <v>42</v>
@@ -1443,10 +1443,10 @@
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>500</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH4" t="n">
         <v>44</v>
@@ -1467,16 +1467,16 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
@@ -1488,10 +1488,10 @@
         <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW4" t="n">
         <v>4.2</v>
@@ -1503,25 +1503,25 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.62</v>
+        <v>3.45</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="BF4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
         <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K5" t="n">
         <v>3.9</v>
@@ -1643,7 +1643,7 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1670,7 +1670,7 @@
         <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1688,7 +1688,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>16</v>
@@ -1724,16 +1724,16 @@
         <v>13</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
         <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS5" t="n">
         <v>28</v>
@@ -1742,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
@@ -1778,7 +1778,7 @@
         <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
         <v>4.2</v>
@@ -1885,7 +1885,7 @@
         <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
@@ -1894,52 +1894,52 @@
         <v>1.4</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X6" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
         <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
         <v>9.4</v>
@@ -1948,7 +1948,7 @@
         <v>20</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF6" t="n">
         <v>14</v>
@@ -1957,7 +1957,7 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
         <v>70</v>
@@ -1969,7 +1969,7 @@
         <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
         <v>320</v>
@@ -1978,31 +1978,31 @@
         <v>15.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR6" t="n">
         <v>14.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
         <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2026,7 +2026,7 @@
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -2139,10 +2139,10 @@
         <v>2.64</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
@@ -2175,7 +2175,7 @@
         <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.48</v>
@@ -2271,7 +2271,7 @@
         <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
@@ -2280,7 +2280,7 @@
         <v>18</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
         <v>16.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.45</v>
@@ -2405,7 +2405,7 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
@@ -2453,7 +2453,7 @@
         <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
         <v>90</v>
@@ -2471,7 +2471,7 @@
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AK8" t="n">
         <v>38</v>
@@ -2534,7 +2534,7 @@
         <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF8" t="n">
         <v>28</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
         <v>1.92</v>
@@ -2647,7 +2647,7 @@
         <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
         <v>3.75</v>
@@ -2659,7 +2659,7 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
@@ -2680,7 +2680,7 @@
         <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G10" t="n">
         <v>1.69</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2913,10 +2913,10 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="P10" t="n">
         <v>3.5</v>
@@ -2931,7 +2931,7 @@
         <v>1.79</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="U10" t="n">
         <v>3.05</v>
@@ -2967,7 +2967,7 @@
         <v>190</v>
       </c>
       <c r="AF10" t="n">
-        <v>500</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
         <v>15.5</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -3143,91 +3143,91 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G11" t="n">
         <v>4.1</v>
       </c>
-      <c r="G11" t="n">
-        <v>4.8</v>
-      </c>
       <c r="H11" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="I11" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O11" t="n">
         <v>1.56</v>
       </c>
-      <c r="M11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.52</v>
-      </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="W11" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD11" t="n">
         <v>13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AG11" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="AI11" t="n">
         <v>460</v>
@@ -3248,67 +3248,67 @@
         <v>500</v>
       </c>
       <c r="AO11" t="n">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB11" t="n">
         <v>10</v>
       </c>
-      <c r="AW11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7</v>
-      </c>
       <c r="BF11" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="BJ11" t="n">
         <v>12</v>
@@ -3323,16 +3323,16 @@
         <v>12</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BO11" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BP11" t="n">
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
@@ -3341,32 +3341,32 @@
         <v>10.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -3415,13 +3415,13 @@
         <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O12" t="n">
         <v>1.44</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -863,7 +863,7 @@
         <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I2" t="n">
         <v>3.7</v>
@@ -992,7 +992,7 @@
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ2" t="n">
         <v>6.6</v>
@@ -1001,7 +1001,7 @@
         <v>8.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BC2" t="n">
         <v>7.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
         <v>1.07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H3" t="n">
         <v>38</v>
@@ -1129,7 +1129,7 @@
         <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
@@ -1156,7 +1156,7 @@
         <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1168,7 +1168,7 @@
         <v>320</v>
       </c>
       <c r="Y3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,13 +1177,13 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>80</v>
       </c>
       <c r="AD3" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1219,7 +1219,7 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -1228,19 +1228,19 @@
         <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>9</v>
       </c>
       <c r="AU3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
@@ -1249,7 +1249,7 @@
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BA3" t="n">
         <v>10.5</v>
@@ -1261,7 +1261,7 @@
         <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE3" t="n">
         <v>10.5</v>
@@ -1273,7 +1273,7 @@
         <v>10.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BI3" t="n">
         <v>5.3</v>
@@ -1288,43 +1288,43 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BP3" t="n">
         <v>5.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT3" t="n">
         <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
         <v>1.62</v>
@@ -1374,7 +1374,7 @@
         <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="n">
         <v>4.3</v>
@@ -1413,22 +1413,22 @@
         <v>1.99</v>
       </c>
       <c r="V4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X4" t="n">
         <v>90</v>
       </c>
       <c r="Y4" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="Z4" t="n">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB4" t="n">
         <v>27</v>
@@ -1437,10 +1437,10 @@
         <v>42</v>
       </c>
       <c r="AD4" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF4" t="n">
         <v>40</v>
@@ -1449,10 +1449,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AH4" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ4" t="n">
         <v>180</v>
@@ -1464,19 +1464,19 @@
         <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AN4" t="n">
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
         <v>6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
@@ -1515,10 +1515,10 @@
         <v>5.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="BF4" t="n">
         <v>4</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1622,16 +1622,16 @@
         <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
         <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K5" t="n">
         <v>3.9</v>
@@ -1652,7 +1652,7 @@
         <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
         <v>1.46</v>
@@ -1670,7 +1670,7 @@
         <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X5" t="n">
         <v>17.5</v>
@@ -1679,7 +1679,7 @@
         <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
         <v>90</v>
@@ -1688,10 +1688,10 @@
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
         <v>44</v>
@@ -1715,7 +1715,7 @@
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
         <v>320</v>
@@ -1727,7 +1727,7 @@
         <v>40</v>
       </c>
       <c r="AP5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>15</v>
@@ -1778,7 +1778,7 @@
         <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
         <v>4.6</v>
@@ -1915,7 +1915,7 @@
         <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
         <v>2.18</v>
@@ -1924,7 +1924,7 @@
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -2002,7 +2002,7 @@
         <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -2133,16 +2133,16 @@
         <v>3.05</v>
       </c>
       <c r="H7" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
@@ -2160,7 +2160,7 @@
         <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R7" t="n">
         <v>1.46</v>
@@ -2172,10 +2172,10 @@
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W7" t="n">
         <v>1.48</v>
@@ -2235,7 +2235,7 @@
         <v>22</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
@@ -2250,7 +2250,7 @@
         <v>10.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
@@ -2271,7 +2271,7 @@
         <v>16</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC7" t="n">
         <v>22</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -2387,13 +2387,13 @@
         <v>2.98</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I8" t="n">
         <v>2.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
@@ -2411,7 +2411,7 @@
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q8" t="n">
         <v>2.12</v>
@@ -2420,19 +2420,19 @@
         <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
         <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V8" t="n">
         <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2522,7 +2522,7 @@
         <v>16</v>
       </c>
       <c r="BA8" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
         <v>18</v>
@@ -2534,7 +2534,7 @@
         <v>23</v>
       </c>
       <c r="BE8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF8" t="n">
         <v>28</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
         <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -2761,7 +2761,7 @@
         <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AW9" t="n">
         <v>4.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -2892,10 +2892,10 @@
         <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
         <v>5.3</v>
@@ -2907,34 +2907,34 @@
         <v>5.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="T10" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="U10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2943,166 +2943,166 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="Y10" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>230</v>
       </c>
       <c r="AA10" t="n">
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AD10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP10" t="n">
         <v>28</v>
       </c>
-      <c r="AE10" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AQ10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BG10" t="n">
         <v>20</v>
       </c>
-      <c r="AG10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>26</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BH10" t="n">
         <v>1000</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="BJ10" t="n">
         <v>12</v>
       </c>
       <c r="BK10" t="n">
-        <v>1.92</v>
+        <v>5.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BN10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP10" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="BR10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="BT10" t="n">
         <v>13</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="BV10" t="n">
         <v>42</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="BX10" t="n">
         <v>40</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -3146,16 +3146,16 @@
         <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>2.32</v>
       </c>
       <c r="I11" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
@@ -3191,7 +3191,7 @@
         <v>1.72</v>
       </c>
       <c r="V11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W11" t="n">
         <v>1.33</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
         <v>1.77</v>
       </c>
       <c r="I12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
@@ -3421,7 +3421,7 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
         <v>1.44</v>
@@ -3433,7 +3433,7 @@
         <v>2.3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
         <v>4.5</v>
@@ -3445,7 +3445,7 @@
         <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
@@ -3568,7 +3568,7 @@
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,7 +3580,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO12" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BP12" t="n">
         <v>1000</v>
@@ -3604,7 +3604,7 @@
         <v>14</v>
       </c>
       <c r="BW12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BX12" t="n">
         <v>36</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,166 +857,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I2" t="n">
         <v>3.15</v>
       </c>
-      <c r="I2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="AA2" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
         <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
         <v>60</v>
       </c>
-      <c r="AF2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
       <c r="AI2" t="n">
-        <v>160</v>
+        <v>370</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT2" t="n">
         <v>5.2</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
         <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD2" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BE2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF2" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BF2" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
@@ -1034,53 +1034,53 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>2.44</v>
+        <v>11.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.32</v>
+        <v>9.6</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>2.3</v>
+        <v>8.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.36</v>
+        <v>9.6</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.32</v>
+        <v>9.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="G3" t="n">
         <v>1.1</v>
@@ -1120,7 +1120,7 @@
         <v>38</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
         <v>16</v>
@@ -1129,46 +1129,46 @@
         <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P3" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Q3" t="n">
         <v>1.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="S3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="X3" t="n">
         <v>320</v>
       </c>
       <c r="Y3" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1183,16 +1183,16 @@
         <v>80</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AH3" t="n">
         <v>330</v>
@@ -1204,82 +1204,82 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK3" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>330</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV3" t="n">
         <v>9</v>
       </c>
-      <c r="AU3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW3" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB3" t="n">
         <v>7.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE3" t="n">
         <v>9.4</v>
       </c>
-      <c r="BE3" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BG3" t="n">
         <v>10.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BJ3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BK3" t="n">
         <v>6.4</v>
@@ -1288,13 +1288,13 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
         <v>5.5</v>
@@ -1303,7 +1303,7 @@
         <v>4.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS3" t="n">
         <v>7</v>
@@ -1318,13 +1318,13 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1365,58 +1365,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P4" t="n">
         <v>2.18</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.67</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.99</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="X4" t="n">
         <v>90</v>
@@ -1431,10 +1431,10 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AD4" t="n">
         <v>500</v>
@@ -1443,10 +1443,10 @@
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AH4" t="n">
         <v>500</v>
@@ -1467,16 +1467,16 @@
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>6</v>
+        <v>2.44</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
@@ -1488,10 +1488,10 @@
         <v>5.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
         <v>4.2</v>
@@ -1503,25 +1503,25 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>2.48</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.2</v>
+        <v>2.16</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.3</v>
+        <v>2.18</v>
       </c>
       <c r="BF4" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
@@ -1530,65 +1530,65 @@
         <v>1000</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BN4" t="n">
         <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1625,25 +1625,25 @@
         <v>2.06</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
         <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1652,19 +1652,19 @@
         <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>1.68</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V5" t="n">
         <v>1.32</v>
@@ -1673,10 +1673,10 @@
         <v>1.94</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
@@ -1688,7 +1688,7 @@
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
         <v>16.5</v>
@@ -1721,10 +1721,10 @@
         <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
@@ -1733,10 +1733,10 @@
         <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1748,13 +1748,13 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>14</v>
@@ -1769,16 +1769,16 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
@@ -1823,7 +1823,7 @@
         <v>5.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BW5" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I6" t="n">
         <v>4.4</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.6</v>
-      </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1897,34 +1897,34 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
         <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
         <v>16.5</v>
@@ -1954,10 +1954,10 @@
         <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
         <v>70</v>
@@ -1981,19 +1981,19 @@
         <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU6" t="n">
         <v>7</v>
@@ -2002,19 +2002,19 @@
         <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
         <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
@@ -2026,31 +2026,31 @@
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BF6" t="n">
         <v>10.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BH6" t="n">
         <v>3.5</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2062,13 +2062,13 @@
         <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BR6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT6" t="n">
         <v>7.6</v>
@@ -2077,16 +2077,16 @@
         <v>5.7</v>
       </c>
       <c r="BV6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX6" t="n">
         <v>44</v>
       </c>
       <c r="BY6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -2127,58 +2127,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="G7" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H7" t="n">
         <v>2.54</v>
       </c>
       <c r="I7" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
         <v>1.46</v>
       </c>
       <c r="S7" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
         <v>21</v>
@@ -2229,7 +2229,7 @@
         <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO7" t="n">
         <v>22</v>
@@ -2256,7 +2256,7 @@
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
         <v>18.5</v>
@@ -2292,19 +2292,19 @@
         <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BJ7" t="n">
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,13 +2316,13 @@
         <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BR7" t="n">
         <v>30</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT7" t="n">
         <v>5.7</v>
@@ -2331,26 +2331,26 @@
         <v>5.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BX7" t="n">
         <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -2384,55 +2384,55 @@
         <v>2.84</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R8" t="n">
         <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
         <v>2.08</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
         <v>13</v>
@@ -2441,16 +2441,16 @@
         <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA8" t="n">
         <v>220</v>
       </c>
       <c r="AB8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
         <v>13</v>
@@ -2459,34 +2459,34 @@
         <v>90</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
       </c>
       <c r="AJ8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM8" t="n">
         <v>500</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AN8" t="n">
         <v>38</v>
       </c>
-      <c r="AL8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>500</v>
-      </c>
       <c r="AO8" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AP8" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>14.5</v>
+        <v>28</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2519,10 +2519,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>18</v>
@@ -2531,19 +2531,19 @@
         <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BF8" t="n">
         <v>28</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BI8" t="n">
         <v>2.54</v>
@@ -2552,13 +2552,13 @@
         <v>10.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>6</v>
@@ -2567,16 +2567,16 @@
         <v>4.4</v>
       </c>
       <c r="BP8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT8" t="n">
         <v>5.9</v>
@@ -2585,16 +2585,16 @@
         <v>4.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="n">
         <v>4.9</v>
@@ -2647,46 +2647,46 @@
         <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
@@ -2707,28 +2707,28 @@
         <v>10</v>
       </c>
       <c r="AD9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>210</v>
+        <v>480</v>
       </c>
       <c r="AF9" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="AJ9" t="n">
         <v>24</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2749,13 +2749,13 @@
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU9" t="n">
         <v>7.2</v>
@@ -2764,7 +2764,7 @@
         <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX9" t="n">
         <v>9.800000000000001</v>
@@ -2773,46 +2773,46 @@
         <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.4</v>
+        <v>60</v>
       </c>
       <c r="BB9" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
@@ -2821,10 +2821,10 @@
         <v>3.4</v>
       </c>
       <c r="BP9" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
@@ -2836,19 +2836,19 @@
         <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>11.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>12</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -2892,43 +2892,43 @@
         <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
         <v>5.3</v>
       </c>
       <c r="J10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O10" t="n">
         <v>1.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="S10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="T10" t="n">
         <v>1.41</v>
@@ -2955,7 +2955,7 @@
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC10" t="n">
         <v>14.5</v>
@@ -2964,10 +2964,10 @@
         <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -3000,7 +3000,7 @@
         <v>28</v>
       </c>
       <c r="AQ10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR10" t="n">
         <v>34</v>
@@ -3051,58 +3051,58 @@
         <v>20</v>
       </c>
       <c r="BH10" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.32</v>
+        <v>4.6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BK10" t="n">
         <v>5.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BM10" t="n">
-        <v>2.26</v>
+        <v>8.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>1.99</v>
+        <v>6.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="BS10" t="n">
-        <v>2.1</v>
+        <v>6.2</v>
       </c>
       <c r="BT10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BU10" t="n">
-        <v>1.98</v>
+        <v>6.2</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.22</v>
+        <v>7.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H11" t="n">
         <v>2.32</v>
       </c>
       <c r="I11" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.25</v>
@@ -3164,10 +3164,10 @@
         <v>1.59</v>
       </c>
       <c r="M11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
@@ -3176,46 +3176,46 @@
         <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA11" t="n">
         <v>50</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
         <v>50</v>
@@ -3224,7 +3224,7 @@
         <v>36</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AH11" t="n">
         <v>36</v>
@@ -3251,19 +3251,19 @@
         <v>120</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS11" t="n">
         <v>22</v>
       </c>
       <c r="AT11" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -3275,28 +3275,28 @@
         <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.800000000000001</v>
+        <v>28</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
       </c>
       <c r="BD11" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE11" t="n">
         <v>10</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
         <v>10.5</v>
@@ -3305,7 +3305,7 @@
         <v>24</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BI11" t="n">
         <v>2.22</v>
@@ -3314,16 +3314,16 @@
         <v>12</v>
       </c>
       <c r="BK11" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO11" t="n">
         <v>5.1</v>
@@ -3332,13 +3332,13 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BT11" t="n">
         <v>5.1</v>
@@ -3347,26 +3347,26 @@
         <v>3.8</v>
       </c>
       <c r="BV11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -3400,52 +3400,52 @@
         <v>5.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="I12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
         <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
         <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
@@ -3454,7 +3454,7 @@
         <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Z12" t="n">
         <v>10.5</v>
@@ -3475,10 +3475,10 @@
         <v>28</v>
       </c>
       <c r="AF12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AG12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AH12" t="n">
         <v>26</v>
@@ -3529,7 +3529,7 @@
         <v>19</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AY12" t="n">
         <v>19</v>
@@ -3538,64 +3538,64 @@
         <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
         <v>12</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BO12" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU12" t="n">
         <v>3.65</v>
@@ -3604,23 +3604,23 @@
         <v>14</v>
       </c>
       <c r="BW12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BX12" t="n">
         <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>34</v>
       </c>
       <c r="CA12" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
         <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
         <v>3.25</v>
@@ -884,13 +884,13 @@
         <v>3.15</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
         <v>1.26</v>
@@ -899,10 +899,10 @@
         <v>4.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V2" t="n">
         <v>1.47</v>
@@ -935,7 +935,7 @@
         <v>120</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
@@ -953,134 +953,134 @@
         <v>75</v>
       </c>
       <c r="AL2" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO2" t="n">
         <v>600</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.4</v>
+        <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AX2" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>7.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="n">
         <v>3.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BO2" t="n">
         <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BT2" t="n">
         <v>6.2</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1117,52 +1117,52 @@
         <v>1.1</v>
       </c>
       <c r="H3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="O3" t="n">
         <v>1.07</v>
       </c>
       <c r="P3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="R3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="X3" t="n">
         <v>320</v>
@@ -1171,19 +1171,19 @@
         <v>160</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AC3" t="n">
         <v>80</v>
       </c>
       <c r="AD3" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1192,43 +1192,43 @@
         <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
         <v>330</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL3" t="n">
         <v>330</v>
       </c>
       <c r="AM3" t="n">
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
         <v>15</v>
@@ -1237,94 +1237,94 @@
         <v>14.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BA3" t="n">
-        <v>9.6</v>
+        <v>13.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE3" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="n">
         <v>7.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BP3" t="n">
         <v>5.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BS3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BU3" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G4" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J4" t="n">
         <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1392,34 +1392,34 @@
         <v>4.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
         <v>1.79</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="U4" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="X4" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1431,10 +1431,10 @@
         <v>700</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AC4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AD4" t="n">
         <v>500</v>
@@ -1443,10 +1443,10 @@
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG4" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AH4" t="n">
         <v>500</v>
@@ -1467,16 +1467,16 @@
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.44</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
         <v>4.2</v>
@@ -1491,7 +1491,7 @@
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW4" t="n">
         <v>4.2</v>
@@ -1503,92 +1503,92 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.48</v>
+        <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.34</v>
+        <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.16</v>
+        <v>3.15</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.64</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.04</v>
+        <v>1.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.04</v>
+        <v>1.57</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.04</v>
+        <v>1.58</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
@@ -1661,28 +1661,28 @@
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U5" t="n">
         <v>2.32</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
@@ -1694,10 +1694,10 @@
         <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1706,7 +1706,7 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
         <v>25</v>
@@ -1715,7 +1715,7 @@
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
         <v>320</v>
@@ -1742,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
@@ -1778,7 +1778,7 @@
         <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1796,16 +1796,16 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BO5" t="n">
         <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>10</v>
@@ -1814,7 +1814,7 @@
         <v>25</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BT5" t="n">
         <v>7.4</v>
@@ -1823,16 +1823,16 @@
         <v>5.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BW5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BX5" t="n">
         <v>38</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
         <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
         <v>4.4</v>
@@ -1888,7 +1888,7 @@
         <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.4</v>
@@ -1897,13 +1897,13 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
         <v>1.92</v>
@@ -1918,7 +1918,7 @@
         <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
         <v>1.29</v>
@@ -1933,13 +1933,13 @@
         <v>18.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA6" t="n">
         <v>110</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
         <v>9.4</v>
@@ -1990,13 +1990,13 @@
         <v>15</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
         <v>15</v>
@@ -2023,16 +2023,16 @@
         <v>18</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
         <v>30</v>
       </c>
       <c r="BF6" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="n">
         <v>3.5</v>
@@ -2044,13 +2044,13 @@
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2059,7 +2059,7 @@
         <v>4.2</v>
       </c>
       <c r="BP6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
         <v>8</v>
@@ -2068,7 +2068,7 @@
         <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT6" t="n">
         <v>7.6</v>
@@ -2080,13 +2080,13 @@
         <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
         <v>4.6</v>
@@ -2157,13 +2157,13 @@
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
         <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -2172,7 +2172,7 @@
         <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V7" t="n">
         <v>1.6</v>
@@ -2181,7 +2181,7 @@
         <v>1.51</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y7" t="n">
         <v>15.5</v>
@@ -2196,7 +2196,7 @@
         <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
         <v>14.5</v>
@@ -2205,7 +2205,7 @@
         <v>32</v>
       </c>
       <c r="AF7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG7" t="n">
         <v>16</v>
@@ -2229,10 +2229,10 @@
         <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP7" t="n">
         <v>15</v>
@@ -2241,52 +2241,52 @@
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AT7" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
         <v>10.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY7" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.4</v>
+        <v>29</v>
       </c>
       <c r="BF7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG7" t="n">
         <v>16.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>15.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.8</v>
@@ -2298,13 +2298,13 @@
         <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BN7" t="n">
         <v>6.2</v>
@@ -2316,13 +2316,13 @@
         <v>21</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>30</v>
       </c>
       <c r="BS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT7" t="n">
         <v>5.7</v>
@@ -2334,7 +2334,7 @@
         <v>18.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX7" t="n">
         <v>28</v>
@@ -2343,14 +2343,14 @@
         <v>10</v>
       </c>
       <c r="BZ7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="CA7" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G8" t="n">
         <v>2.96</v>
@@ -2399,19 +2399,19 @@
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
         <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
         <v>2.22</v>
@@ -2423,10 +2423,10 @@
         <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
         <v>1.53</v>
@@ -2486,7 +2486,7 @@
         <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>10</v>
@@ -2495,7 +2495,7 @@
         <v>8.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
         <v>36</v>
@@ -2504,7 +2504,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2522,10 +2522,10 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC8" t="n">
         <v>25</v>
@@ -2534,13 +2534,13 @@
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
         <v>28</v>
       </c>
       <c r="BG8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH8" t="n">
         <v>3.2</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
         <v>1.46</v>
@@ -2665,7 +2665,7 @@
         <v>1.39</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
         <v>2.2</v>
@@ -2677,7 +2677,7 @@
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
         <v>1.94</v>
@@ -2686,7 +2686,7 @@
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
         <v>14.5</v>
@@ -2695,7 +2695,7 @@
         <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
@@ -2719,16 +2719,16 @@
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>95</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
         <v>500</v>
@@ -2737,7 +2737,7 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>700</v>
@@ -2746,13 +2746,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2764,13 +2764,13 @@
         <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.1</v>
+        <v>60</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>17.5</v>
@@ -2782,73 +2782,73 @@
         <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BF9" t="n">
         <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BP9" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9" t="n">
         <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -2892,19 +2892,19 @@
         <v>1.62</v>
       </c>
       <c r="G10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>5.3</v>
       </c>
       <c r="J10" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
         <v>1.19</v>
@@ -2919,7 +2919,7 @@
         <v>1.1</v>
       </c>
       <c r="P10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>1.32</v>
@@ -2928,10 +2928,10 @@
         <v>2.22</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="T10" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="U10" t="n">
         <v>3.2</v>
@@ -2946,7 +2946,7 @@
         <v>55</v>
       </c>
       <c r="Y10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z10" t="n">
         <v>230</v>
@@ -2961,7 +2961,7 @@
         <v>14.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
         <v>55</v>
@@ -2973,10 +2973,10 @@
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
         <v>23</v>
@@ -2985,31 +2985,31 @@
         <v>15.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AM10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AQ10" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AR10" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AS10" t="n">
         <v>29</v>
       </c>
       <c r="AT10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AU10" t="n">
         <v>12.5</v>
@@ -3018,7 +3018,7 @@
         <v>19</v>
       </c>
       <c r="AW10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
         <v>16</v>
@@ -3033,13 +3033,13 @@
         <v>25</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BE10" t="n">
         <v>27</v>
@@ -3054,7 +3054,7 @@
         <v>6.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>9</v>
@@ -3066,13 +3066,13 @@
         <v>75</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BN10" t="n">
         <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP10" t="n">
         <v>10.5</v>
@@ -3081,10 +3081,10 @@
         <v>6.6</v>
       </c>
       <c r="BR10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BS10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT10" t="n">
         <v>10</v>
@@ -3096,13 +3096,13 @@
         <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -3143,13 +3143,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="I11" t="n">
         <v>2.42</v>
@@ -3164,7 +3164,7 @@
         <v>1.59</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
         <v>2.62</v>
@@ -3185,10 +3185,10 @@
         <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="V11" t="n">
         <v>1.71</v>
@@ -3197,13 +3197,13 @@
         <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
         <v>50</v>
@@ -3224,7 +3224,7 @@
         <v>36</v>
       </c>
       <c r="AG11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
         <v>36</v>
@@ -3236,7 +3236,7 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
@@ -3263,7 +3263,7 @@
         <v>22</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -3296,34 +3296,34 @@
         <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
         <v>24</v>
       </c>
       <c r="BH11" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>10.5</v>
+        <v>2.28</v>
       </c>
       <c r="BN11" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BO11" t="n">
         <v>5.1</v>
@@ -3332,41 +3332,41 @@
         <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BT11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BU11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
         <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="I12" t="n">
         <v>1.87</v>
@@ -3475,10 +3475,10 @@
         <v>28</v>
       </c>
       <c r="AF12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AG12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH12" t="n">
         <v>26</v>
@@ -3526,10 +3526,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.7</v>
+        <v>32</v>
       </c>
       <c r="AY12" t="n">
         <v>19</v>
@@ -3538,25 +3538,25 @@
         <v>21</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.8</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC12" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC12" t="n">
-        <v>6</v>
-      </c>
       <c r="BD12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF12" t="n">
         <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BH12" t="n">
         <v>3.05</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN12" t="n">
         <v>9.199999999999999</v>
@@ -3583,19 +3583,19 @@
         <v>6.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU12" t="n">
         <v>3.65</v>
@@ -3610,17 +3610,17 @@
         <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>34</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,82 +857,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G2" t="n">
         <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U2" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
       </c>
       <c r="X2" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
         <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -941,16 +941,16 @@
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>85</v>
       </c>
       <c r="AK2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -968,7 +968,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
         <v>16</v>
@@ -995,79 +995,79 @@
         <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
       </c>
       <c r="BC2" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
         <v>29</v>
       </c>
       <c r="BE2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="BG2" t="n">
         <v>36</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
         <v>4.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
         <v>11</v>
@@ -1076,11 +1076,11 @@
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1120,13 +1120,13 @@
         <v>40</v>
       </c>
       <c r="I3" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.16</v>
@@ -1141,16 +1141,16 @@
         <v>1.07</v>
       </c>
       <c r="P3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
         <v>1.24</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T3" t="n">
         <v>2.28</v>
@@ -1162,16 +1162,16 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="X3" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="Z3" t="n">
-        <v>470</v>
+        <v>590</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1180,10 +1180,10 @@
         <v>21</v>
       </c>
       <c r="AC3" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1195,13 +1195,13 @@
         <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>330</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="n">
-        <v>420</v>
+        <v>490</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AK3" t="n">
         <v>16</v>
@@ -1210,7 +1210,7 @@
         <v>330</v>
       </c>
       <c r="AM3" t="n">
-        <v>340</v>
+        <v>370</v>
       </c>
       <c r="AN3" t="n">
         <v>2.08</v>
@@ -1219,10 +1219,10 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>13.5</v>
@@ -1231,7 +1231,7 @@
         <v>14</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AU3" t="n">
         <v>14.5</v>
@@ -1243,7 +1243,7 @@
         <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY3" t="n">
         <v>15.5</v>
@@ -1255,19 +1255,19 @@
         <v>13.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
@@ -1276,19 +1276,19 @@
         <v>7.2</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
@@ -1297,7 +1297,7 @@
         <v>3.75</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BQ3" t="n">
         <v>4.7</v>
@@ -1309,22 +1309,22 @@
         <v>7.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.65</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="H4" t="n">
         <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
         <v>4.2</v>
@@ -1389,37 +1389,37 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.25</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T4" t="n">
         <v>1.79</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
         <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X4" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1470,16 +1470,16 @@
         <v>27</v>
       </c>
       <c r="AO4" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
         <v>4.2</v>
@@ -1491,7 +1491,7 @@
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
         <v>4.2</v>
@@ -1503,7 +1503,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BA4" t="n">
         <v>4.2</v>
@@ -1515,13 +1515,13 @@
         <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.44</v>
+        <v>3.75</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
@@ -1530,65 +1530,65 @@
         <v>4</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>1000</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="BN4" t="n">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.7</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
@@ -1655,31 +1655,31 @@
         <v>1.8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
         <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
         <v>160</v>
@@ -1688,16 +1688,16 @@
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
         <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1709,7 +1709,7 @@
         <v>110</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK5" t="n">
         <v>21</v>
@@ -1721,7 +1721,7 @@
         <v>320</v>
       </c>
       <c r="AN5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
         <v>46</v>
@@ -1748,7 +1748,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1757,7 +1757,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
         <v>32</v>
@@ -1769,16 +1769,16 @@
         <v>17.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE5" t="n">
         <v>34</v>
       </c>
       <c r="BF5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BH5" t="n">
         <v>3.8</v>
@@ -1796,16 +1796,16 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO5" t="n">
         <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ5" t="n">
         <v>10</v>
@@ -1817,7 +1817,7 @@
         <v>10.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU5" t="n">
         <v>5.4</v>
@@ -1826,13 +1826,13 @@
         <v>40</v>
       </c>
       <c r="BW5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1873,61 +1873,61 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.65</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T6" t="n">
         <v>1.73</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
         <v>18.5</v>
@@ -1942,7 +1942,7 @@
         <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD6" t="n">
         <v>20</v>
@@ -1951,31 +1951,31 @@
         <v>55</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
         <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO6" t="n">
         <v>60</v>
@@ -1984,73 +1984,73 @@
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
         <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="BB6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>16.5</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BF6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BN6" t="n">
         <v>4.7</v>
@@ -2062,13 +2062,13 @@
         <v>13.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BR6" t="n">
         <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT6" t="n">
         <v>7.6</v>
@@ -2080,13 +2080,13 @@
         <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX6" t="n">
         <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.86</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.96</v>
-      </c>
       <c r="H7" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="I7" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.36</v>
@@ -2169,16 +2169,16 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X7" t="n">
         <v>22</v>
@@ -2187,7 +2187,7 @@
         <v>15.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
         <v>44</v>
@@ -2196,13 +2196,13 @@
         <v>16.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
         <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
         <v>25</v>
@@ -2220,7 +2220,7 @@
         <v>55</v>
       </c>
       <c r="AK7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
@@ -2235,34 +2235,34 @@
         <v>20</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>16.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AT7" t="n">
         <v>12.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
         <v>13.5</v>
@@ -2277,55 +2277,55 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BF7" t="n">
         <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="n">
         <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO7" t="n">
         <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU7" t="n">
         <v>5.1</v>
@@ -2334,23 +2334,23 @@
         <v>18.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BX7" t="n">
         <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
         <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I8" t="n">
         <v>2.86</v>
@@ -2399,13 +2399,13 @@
         <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O8" t="n">
         <v>1.39</v>
@@ -2414,19 +2414,19 @@
         <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
         <v>1.53</v>
@@ -2435,7 +2435,7 @@
         <v>1.51</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
         <v>10.5</v>
@@ -2450,10 +2450,10 @@
         <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE8" t="n">
         <v>90</v>
@@ -2465,7 +2465,7 @@
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
         <v>500</v>
@@ -2474,7 +2474,7 @@
         <v>48</v>
       </c>
       <c r="AK8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2489,7 +2489,7 @@
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>8.6</v>
@@ -2504,7 +2504,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2513,7 +2513,7 @@
         <v>28</v>
       </c>
       <c r="AX8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
@@ -2525,34 +2525,34 @@
         <v>26</v>
       </c>
       <c r="BB8" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BD8" t="n">
         <v>36</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
         <v>28</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.54</v>
+        <v>2.94</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2561,7 +2561,7 @@
         <v>10.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BO8" t="n">
         <v>4.4</v>
@@ -2570,16 +2570,16 @@
         <v>24</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BU8" t="n">
         <v>4.3</v>
@@ -2588,13 +2588,13 @@
         <v>23</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -2635,34 +2635,34 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="n">
         <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
         <v>1.8</v>
@@ -2674,133 +2674,133 @@
         <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK9" t="n">
         <v>42</v>
       </c>
-      <c r="AA9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>480</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>22</v>
-      </c>
       <c r="AL9" t="n">
-        <v>500</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>32</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.8</v>
+        <v>15.5</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW9" t="n">
         <v>60</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB9" t="n">
         <v>17.5</v>
       </c>
-      <c r="BA9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>17</v>
-      </c>
       <c r="BC9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.8</v>
+        <v>80</v>
       </c>
       <c r="BH9" t="n">
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
@@ -2812,13 +2812,13 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP9" t="n">
         <v>13.5</v>
@@ -2830,10 +2830,10 @@
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU9" t="n">
         <v>5.5</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -2913,7 +2913,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
         <v>1.1</v>
@@ -2922,19 +2922,19 @@
         <v>4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="R10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="S10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2958,7 +2958,7 @@
         <v>23</v>
       </c>
       <c r="AC10" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
         <v>23</v>
@@ -2973,13 +2973,13 @@
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
         <v>15.5</v>
@@ -2991,13 +2991,13 @@
         <v>40</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AO10" t="n">
         <v>24</v>
       </c>
       <c r="AP10" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AQ10" t="n">
         <v>34</v>
@@ -3012,7 +3012,7 @@
         <v>19.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AV10" t="n">
         <v>19</v>
@@ -3027,10 +3027,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
         <v>18.5</v>
@@ -3042,10 +3042,10 @@
         <v>17.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BG10" t="n">
         <v>20</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.15</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.25</v>
       </c>
       <c r="L11" t="n">
         <v>1.59</v>
@@ -3176,7 +3176,7 @@
         <v>1.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
@@ -3191,7 +3191,7 @@
         <v>1.77</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
         <v>1.35</v>
@@ -3281,7 +3281,7 @@
         <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
         <v>28</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="I12" t="n">
         <v>1.87</v>
       </c>
       <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.45</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3421,13 +3421,13 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
         <v>2.4</v>
@@ -3460,10 +3460,10 @@
         <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.6</v>
@@ -3526,7 +3526,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX12" t="n">
         <v>32</v>
@@ -3535,25 +3535,25 @@
         <v>19</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>36</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG12" t="n">
         <v>14.5</v>
@@ -3562,7 +3562,7 @@
         <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN12" t="n">
         <v>9.199999999999999</v>
@@ -3586,16 +3586,16 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU12" t="n">
         <v>3.65</v>
@@ -3604,23 +3604,23 @@
         <v>14</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX12" t="n">
         <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>34</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,19 +857,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
@@ -881,31 +881,31 @@
         <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W2" t="n">
         <v>1.58</v>
@@ -914,25 +914,25 @@
         <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>7.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>230</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -941,10 +941,10 @@
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
         <v>85</v>
@@ -962,28 +962,28 @@
         <v>600</v>
       </c>
       <c r="AO2" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AS2" t="n">
         <v>42</v>
       </c>
       <c r="AT2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
         <v>34</v>
@@ -995,22 +995,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="BD2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
         <v>30</v>
@@ -1022,65 +1022,65 @@
         <v>3.05</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BK2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>10</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1111,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="H3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I3" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="K3" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="L3" t="n">
         <v>1.16</v>
@@ -1144,34 +1144,34 @@
         <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R3" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="S3" t="n">
         <v>1.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Y3" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="Z3" t="n">
-        <v>590</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
@@ -1180,10 +1180,10 @@
         <v>21</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AD3" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1198,7 +1198,7 @@
         <v>85</v>
       </c>
       <c r="AI3" t="n">
-        <v>490</v>
+        <v>560</v>
       </c>
       <c r="AJ3" t="n">
         <v>9.199999999999999</v>
@@ -1210,16 +1210,16 @@
         <v>330</v>
       </c>
       <c r="AM3" t="n">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
@@ -1228,7 +1228,7 @@
         <v>13.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT3" t="n">
         <v>17</v>
@@ -1240,7 +1240,7 @@
         <v>12.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AX3" t="n">
         <v>9.800000000000001</v>
@@ -1249,13 +1249,13 @@
         <v>15.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
         <v>13.5</v>
@@ -1264,19 +1264,19 @@
         <v>11.5</v>
       </c>
       <c r="BE3" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BG3" t="n">
         <v>13.5</v>
       </c>
-      <c r="BF3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>14</v>
-      </c>
       <c r="BH3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BJ3" t="n">
         <v>18</v>
@@ -1288,22 +1288,22 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BP3" t="n">
         <v>5.4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS3" t="n">
         <v>7.4</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>1.59</v>
       </c>
       <c r="G4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
         <v>7.2</v>
@@ -1389,22 +1389,22 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="R4" t="n">
         <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="T4" t="n">
         <v>1.79</v>
@@ -1416,10 +1416,10 @@
         <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y4" t="n">
         <v>500</v>
@@ -1479,7 +1479,7 @@
         <v>10.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AS4" t="n">
         <v>4.2</v>
@@ -1515,13 +1515,13 @@
         <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BG4" t="n">
         <v>4.2</v>
@@ -1542,7 +1542,7 @@
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="BN4" t="n">
         <v>4.3</v>
@@ -1554,41 +1554,41 @@
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>8</v>
+        <v>4.1</v>
       </c>
       <c r="BT4" t="n">
         <v>1000</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1643,25 +1643,25 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
         <v>2.36</v>
@@ -1670,7 +1670,7 @@
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
@@ -1679,22 +1679,22 @@
         <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AA5" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AF5" t="n">
         <v>14.5</v>
@@ -1706,7 +1706,7 @@
         <v>16</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
         <v>26</v>
@@ -1715,16 +1715,16 @@
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>320</v>
+        <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
@@ -1733,10 +1733,10 @@
         <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1748,31 +1748,31 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>26</v>
       </c>
       <c r="BE5" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF5" t="n">
         <v>11</v>
@@ -1781,10 +1781,10 @@
         <v>30</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
@@ -1796,43 +1796,43 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BN5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BO5" t="n">
         <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ5" t="n">
         <v>10</v>
       </c>
       <c r="BR5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BS5" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU5" t="n">
         <v>5.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="BW5" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1873,10 +1873,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G6" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
@@ -1885,10 +1885,10 @@
         <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1900,100 +1900,100 @@
         <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="X6" t="n">
         <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC6" t="n">
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI6" t="n">
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM6" t="n">
         <v>90</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS6" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
         <v>7.6</v>
@@ -2014,19 +2014,19 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB6" t="n">
         <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD6" t="n">
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BF6" t="n">
         <v>12</v>
@@ -2044,31 +2044,31 @@
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR6" t="n">
         <v>27</v>
       </c>
       <c r="BS6" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6" t="n">
         <v>7.6</v>
@@ -2080,13 +2080,13 @@
         <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BX6" t="n">
         <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G7" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J7" t="n">
         <v>3.65</v>
@@ -2148,7 +2148,7 @@
         <v>1.36</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
         <v>4.6</v>
@@ -2163,7 +2163,7 @@
         <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -2172,118 +2172,118 @@
         <v>1.65</v>
       </c>
       <c r="U7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN7" t="n">
         <v>22</v>
       </c>
-      <c r="Y7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG7" t="n">
+      <c r="AO7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP7" t="n">
         <v>16</v>
       </c>
-      <c r="AH7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AQ7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT7" t="n">
         <v>12</v>
       </c>
-      <c r="AR7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AU7" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY7" t="n">
         <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BG7" t="n">
         <v>17</v>
@@ -2295,62 +2295,62 @@
         <v>3.15</v>
       </c>
       <c r="BJ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BK7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN7" t="n">
         <v>6</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BR7" t="n">
         <v>29</v>
       </c>
       <c r="BS7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT7" t="n">
         <v>5.8</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV7" t="n">
         <v>18.5</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7" t="n">
         <v>28</v>
       </c>
       <c r="BY7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -2381,73 +2381,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="I8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T8" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.83</v>
-      </c>
       <c r="U8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V8" t="n">
         <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
@@ -2456,7 +2456,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="n">
         <v>19</v>
@@ -2465,10 +2465,10 @@
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
         <v>48</v>
@@ -2489,22 +2489,22 @@
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS8" t="n">
         <v>36</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
@@ -2519,82 +2519,82 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
       </c>
       <c r="BC8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE8" t="n">
         <v>30</v>
       </c>
-      <c r="BD8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BF8" t="n">
-        <v>28</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="BJ8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
         <v>10</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.9</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
         <v>24</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>23</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -2635,25 +2635,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
         <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
         <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
         <v>1.09</v>
@@ -2671,13 +2671,13 @@
         <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U9" t="n">
         <v>1.93</v>
@@ -2686,43 +2686,43 @@
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>210</v>
+        <v>480</v>
       </c>
       <c r="AF9" t="n">
         <v>10.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>380</v>
       </c>
       <c r="AJ9" t="n">
         <v>20</v>
@@ -2731,16 +2731,16 @@
         <v>42</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN9" t="n">
         <v>17.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP9" t="n">
         <v>10.5</v>
@@ -2752,7 +2752,7 @@
         <v>32</v>
       </c>
       <c r="AS9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2770,7 +2770,7 @@
         <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
@@ -2788,67 +2788,67 @@
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG9" t="n">
         <v>14</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>80</v>
       </c>
       <c r="BH9" t="n">
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
         <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>13</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G10" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H10" t="n">
         <v>5</v>
@@ -2901,40 +2901,40 @@
         <v>5.3</v>
       </c>
       <c r="J10" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M10" t="n">
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="R10" t="n">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="S10" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="T10" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="U10" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2943,166 +2943,166 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="Y10" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="Z10" t="n">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="AA10" t="n">
         <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AC10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
         <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AM10" t="n">
         <v>40</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="AO10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>24</v>
       </c>
-      <c r="AP10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>34</v>
-      </c>
       <c r="AR10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AS10" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AT10" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>36</v>
       </c>
       <c r="AX10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
         <v>12.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE10" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BF10" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BI10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BJ10" t="n">
         <v>9</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL10" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="BM10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BT10" t="n">
         <v>10.5</v>
       </c>
-      <c r="BQ10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>10</v>
-      </c>
       <c r="BU10" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV10" t="n">
         <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BX10" t="n">
         <v>28</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H11" t="n">
         <v>2.34</v>
@@ -3155,10 +3155,10 @@
         <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.59</v>
@@ -3173,19 +3173,19 @@
         <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
         <v>2.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
         <v>1.77</v>
@@ -3197,22 +3197,22 @@
         <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
         <v>7.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
         <v>12.5</v>
@@ -3221,7 +3221,7 @@
         <v>50</v>
       </c>
       <c r="AF11" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AG11" t="n">
         <v>16</v>
@@ -3233,76 +3233,76 @@
         <v>460</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK11" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AO11" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>22</v>
       </c>
-      <c r="AT11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>16</v>
-      </c>
       <c r="BA11" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="BC11" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="BD11" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE11" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BG11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BH11" t="n">
         <v>2.68</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -3397,13 +3397,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G12" t="n">
         <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I12" t="n">
         <v>1.87</v>
@@ -3421,19 +3421,19 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
         <v>1.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
         <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
         <v>4.7</v>
@@ -3442,7 +3442,7 @@
         <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
         <v>2.14</v>
@@ -3451,118 +3451,118 @@
         <v>1.2</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
         <v>7</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB12" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AG12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
       </c>
       <c r="AJ12" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM12" t="n">
         <v>210</v>
       </c>
-      <c r="AK12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>130</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>220</v>
-      </c>
       <c r="AN12" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB12" t="n">
         <v>13</v>
       </c>
-      <c r="AU12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC12" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.8</v>
+        <v>13.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH12" t="n">
         <v>3.05</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ12" t="n">
         <v>12</v>
@@ -3574,25 +3574,25 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BO12" t="n">
         <v>6.6</v>
       </c>
       <c r="BP12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>80</v>
+      </c>
+      <c r="BS12" t="n">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>10</v>
       </c>
       <c r="BT12" t="n">
         <v>4.3</v>
@@ -3604,23 +3604,23 @@
         <v>14</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX12" t="n">
         <v>36</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>34</v>
       </c>
       <c r="CA12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,10 +860,10 @@
         <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
         <v>3.15</v>
@@ -875,7 +875,7 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -887,10 +887,10 @@
         <v>1.43</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
@@ -899,40 +899,40 @@
         <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V2" t="n">
         <v>1.47</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
         <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="n">
         <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
         <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -941,79 +941,79 @@
         <v>12.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AM2" t="n">
-        <v>580</v>
+        <v>620</v>
       </c>
       <c r="AN2" t="n">
-        <v>600</v>
+        <v>42</v>
       </c>
       <c r="AO2" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="BC2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="BF2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BG2" t="n">
         <v>36</v>
@@ -1028,13 +1028,13 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN2" t="n">
         <v>5.5</v>
@@ -1043,44 +1043,44 @@
         <v>4.9</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BU2" t="n">
         <v>5.3</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA2" t="n">
         <v>11.5</v>
       </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -1117,46 +1117,46 @@
         <v>1.09</v>
       </c>
       <c r="H3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I3" t="n">
         <v>60</v>
       </c>
       <c r="J3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="K3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="R3" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1165,10 +1165,10 @@
         <v>12</v>
       </c>
       <c r="X3" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="Y3" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,154 +1177,154 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC3" t="n">
         <v>48</v>
       </c>
       <c r="AD3" t="n">
-        <v>190</v>
+        <v>560</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="n">
-        <v>560</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>330</v>
+        <v>70</v>
       </c>
       <c r="AM3" t="n">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AQ3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV3" t="n">
         <v>13</v>
       </c>
-      <c r="AR3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AW3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ3" t="n">
         <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="BG3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BJ3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT3" t="n">
         <v>32</v>
       </c>
       <c r="BU3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY3" t="n">
         <v>11</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>10.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -1365,91 +1365,91 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S4" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="X4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="Z4" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AA4" t="n">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI4" t="n">
         <v>700</v>
@@ -1458,7 +1458,7 @@
         <v>180</v>
       </c>
       <c r="AK4" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AL4" t="n">
         <v>500</v>
@@ -1467,118 +1467,118 @@
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP4" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BB4" t="n">
         <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="BE4" t="n">
-        <v>4</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BI4" t="n">
         <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BP4" t="n">
         <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>4.1</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -1619,22 +1619,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
@@ -1643,34 +1643,34 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
         <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
         <v>2.36</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
@@ -1679,10 +1679,10 @@
         <v>17.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
         <v>11.5</v>
@@ -1691,10 +1691,10 @@
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
         <v>14.5</v>
@@ -1721,7 +1721,7 @@
         <v>85</v>
       </c>
       <c r="AN5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO5" t="n">
         <v>40</v>
@@ -1730,7 +1730,7 @@
         <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
         <v>26</v>
@@ -1754,13 +1754,13 @@
         <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
         <v>14</v>
       </c>
       <c r="BA5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
         <v>22</v>
@@ -1784,7 +1784,7 @@
         <v>3.85</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
@@ -1796,25 +1796,25 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO5" t="n">
         <v>4.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ5" t="n">
         <v>10</v>
       </c>
       <c r="BR5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT5" t="n">
         <v>7.4</v>
@@ -1826,13 +1826,13 @@
         <v>29</v>
       </c>
       <c r="BW5" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -1873,28 +1873,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
         <v>4.3</v>
@@ -1915,19 +1915,19 @@
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
         <v>2.24</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
         <v>17</v>
@@ -1954,13 +1954,13 @@
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
         <v>23</v>
@@ -1978,10 +1978,10 @@
         <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>15</v>
@@ -1990,7 +1990,7 @@
         <v>28</v>
       </c>
       <c r="AS6" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="AT6" t="n">
         <v>9.4</v>
@@ -2017,7 +2017,7 @@
         <v>48</v>
       </c>
       <c r="BB6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC6" t="n">
         <v>18</v>
@@ -2026,13 +2026,13 @@
         <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="BF6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH6" t="n">
         <v>3.6</v>
@@ -2041,16 +2041,16 @@
         <v>3.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
@@ -2062,13 +2062,13 @@
         <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT6" t="n">
         <v>7.6</v>
@@ -2080,13 +2080,13 @@
         <v>34</v>
       </c>
       <c r="BW6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX6" t="n">
         <v>42</v>
       </c>
       <c r="BY6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -2127,88 +2127,88 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
-        <v>2.84</v>
+        <v>2.54</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.26</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
         <v>2.44</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="W7" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD7" t="n">
         <v>12.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
         <v>15.5</v>
@@ -2217,127 +2217,127 @@
         <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
         <v>70</v>
       </c>
       <c r="AN7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO7" t="n">
         <v>22</v>
       </c>
-      <c r="AO7" t="n">
-        <v>19</v>
-      </c>
       <c r="AP7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="BF7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BH7" t="n">
         <v>3.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BL7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BM7" t="n">
         <v>15</v>
       </c>
       <c r="BN7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS7" t="n">
         <v>11</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BU7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY7" t="n">
         <v>11</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -2393,10 +2393,10 @@
         <v>2.88</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
         <v>1.46</v>
@@ -2405,22 +2405,22 @@
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
         <v>1.81</v>
@@ -2441,10 +2441,10 @@
         <v>11.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="AB8" t="n">
         <v>11.5</v>
@@ -2453,19 +2453,19 @@
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
         <v>50</v>
@@ -2480,7 +2480,7 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
         <v>38</v>
@@ -2489,19 +2489,19 @@
         <v>600</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS8" t="n">
         <v>36</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
@@ -2513,16 +2513,16 @@
         <v>28</v>
       </c>
       <c r="AX8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
         <v>20</v>
@@ -2534,10 +2534,10 @@
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.6</v>
+        <v>27</v>
       </c>
       <c r="BG8" t="n">
         <v>8.4</v>
@@ -2546,43 +2546,43 @@
         <v>3.45</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO8" t="n">
         <v>4.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV8" t="n">
         <v>23</v>
@@ -2591,10 +2591,10 @@
         <v>15.5</v>
       </c>
       <c r="BX8" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.9</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
         <v>5.3</v>
@@ -2650,7 +2650,7 @@
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.47</v>
@@ -2671,37 +2671,37 @@
         <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
         <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z9" t="n">
         <v>38</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
@@ -2710,19 +2710,19 @@
         <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>480</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="n">
         <v>10.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH9" t="n">
         <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>380</v>
+        <v>200</v>
       </c>
       <c r="AJ9" t="n">
         <v>20</v>
@@ -2734,16 +2734,16 @@
         <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>150</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
         <v>110</v>
       </c>
       <c r="AP9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ9" t="n">
         <v>14.5</v>
@@ -2752,31 +2752,31 @@
         <v>32</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AT9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU9" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>17.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY9" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9</v>
       </c>
       <c r="AZ9" t="n">
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BB9" t="n">
         <v>17.5</v>
@@ -2785,52 +2785,52 @@
         <v>18.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BF9" t="n">
         <v>13.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="BH9" t="n">
         <v>3.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP9" t="n">
         <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT9" t="n">
         <v>8.4</v>
@@ -2842,13 +2842,13 @@
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -2889,19 +2889,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K10" t="n">
         <v>5.7</v>
@@ -2913,25 +2913,25 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="O10" t="n">
         <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R10" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="S10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="T10" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="U10" t="n">
         <v>3.35</v>
@@ -2943,10 +2943,10 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="Y10" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="Z10" t="n">
         <v>70</v>
@@ -2958,13 +2958,13 @@
         <v>26</v>
       </c>
       <c r="AC10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2973,136 +2973,136 @@
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AM10" t="n">
         <v>40</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AO10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT10" t="n">
         <v>23</v>
       </c>
-      <c r="AP10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>21</v>
-      </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AX10" t="n">
         <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="BG10" t="n">
         <v>19.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BJ10" t="n">
         <v>9</v>
       </c>
       <c r="BK10" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BL10" t="n">
         <v>48</v>
       </c>
       <c r="BM10" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BN10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BO10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BP10" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BR10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BS10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BT10" t="n">
         <v>10.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BV10" t="n">
         <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="BX10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BY10" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
         <v>2.34</v>
       </c>
       <c r="I11" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -3167,49 +3167,49 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T11" t="n">
         <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="W11" t="n">
         <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y11" t="n">
         <v>7.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA11" t="n">
         <v>36</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
         <v>7.6</v>
@@ -3227,7 +3227,7 @@
         <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>460</v>
@@ -3242,16 +3242,16 @@
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
         <v>110</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.8</v>
@@ -3272,37 +3272,37 @@
         <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>21</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>22</v>
       </c>
       <c r="BA11" t="n">
         <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BC11" t="n">
         <v>42</v>
       </c>
       <c r="BD11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE11" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF11" t="n">
         <v>44</v>
       </c>
       <c r="BG11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BH11" t="n">
         <v>2.68</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="I12" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -3424,28 +3424,28 @@
         <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P12" t="n">
         <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R12" t="n">
         <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
         <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="W12" t="n">
         <v>1.2</v>
@@ -3469,7 +3469,7 @@
         <v>8</v>
       </c>
       <c r="AD12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>24</v>
@@ -3496,7 +3496,7 @@
         <v>120</v>
       </c>
       <c r="AM12" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN12" t="n">
         <v>160</v>
@@ -3508,7 +3508,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AR12" t="n">
         <v>8.800000000000001</v>
@@ -3541,19 +3541,19 @@
         <v>44</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="BD12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BF12" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG12" t="n">
         <v>15</v>
@@ -3577,7 +3577,7 @@
         <v>10.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO12" t="n">
         <v>6.6</v>
@@ -3586,16 +3586,16 @@
         <v>65</v>
       </c>
       <c r="BQ12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BR12" t="n">
         <v>80</v>
       </c>
       <c r="BS12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BU12" t="n">
         <v>3.65</v>
@@ -3620,7 +3620,261 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Argentinian Torneo A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:15:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>9 de Julio Rafaela</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Club Atletico el Linqueno</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>2.76</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>2.86</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.43</v>
+        <v>1.8</v>
       </c>
       <c r="P2" t="n">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.32</v>
+        <v>3.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="S2" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.93</v>
+        <v>2.58</v>
       </c>
       <c r="U2" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="V2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="Z2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>70</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>23</v>
       </c>
-      <c r="AA2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="BK2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
         <v>7.6</v>
       </c>
-      <c r="AD2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>620</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BK2" t="n">
+      <c r="BN2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>910</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW2" t="n">
         <v>8.4</v>
       </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="BY2" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="CA2" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -1111,64 +1111,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="G3" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="H3" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="I3" t="n">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="J3" t="n">
-        <v>16.5</v>
+        <v>42</v>
       </c>
       <c r="K3" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="L3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>15</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.69</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="X3" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1177,154 +1177,154 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AC3" t="n">
-        <v>48</v>
+        <v>610</v>
       </c>
       <c r="AD3" t="n">
-        <v>560</v>
+        <v>880</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>880</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>990</v>
       </c>
       <c r="AH3" t="n">
-        <v>75</v>
+        <v>990</v>
       </c>
       <c r="AI3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>980</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AK3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AR3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AS3" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AT3" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AU3" t="n">
-        <v>28</v>
+        <v>2.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>1.53</v>
       </c>
       <c r="AY3" t="n">
-        <v>16.5</v>
+        <v>1.61</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>2.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>13.5</v>
+        <v>140</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>1.57</v>
       </c>
       <c r="BD3" t="n">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="BE3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BI3" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BJ3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="BK3" t="n">
-        <v>10.5</v>
+        <v>1.02</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="BM3" t="n">
-        <v>11</v>
+        <v>1.02</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.2</v>
+        <v>880</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="BR3" t="n">
-        <v>20</v>
+        <v>910</v>
       </c>
       <c r="BS3" t="n">
-        <v>7.8</v>
+        <v>1.02</v>
       </c>
       <c r="BT3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BU3" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="G4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
         <v>6.4</v>
@@ -1380,7 +1380,7 @@
         <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.34</v>
@@ -1407,10 +1407,10 @@
         <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V4" t="n">
         <v>1.19</v>
@@ -1419,112 +1419,112 @@
         <v>2.38</v>
       </c>
       <c r="X4" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="Y4" t="n">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="Z4" t="n">
-        <v>220</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
         <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="AE4" t="n">
         <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AI4" t="n">
         <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>180</v>
+        <v>19.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AM4" t="n">
         <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="AT4" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC4" t="n">
         <v>13</v>
       </c>
-      <c r="AW4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX4" t="n">
+      <c r="BD4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG4" t="n">
         <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
         <v>4.1</v>
@@ -1533,37 +1533,37 @@
         <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BU4" t="n">
         <v>7.6</v>
@@ -1572,23 +1572,23 @@
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>2.04</v>
       </c>
       <c r="G5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H5" t="n">
         <v>3.9</v>
@@ -1634,7 +1634,7 @@
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
@@ -1643,7 +1643,7 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
@@ -1652,46 +1652,46 @@
         <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V5" t="n">
         <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z5" t="n">
         <v>32</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE5" t="n">
         <v>46</v>
@@ -1703,100 +1703,100 @@
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK5" t="n">
         <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
         <v>12.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS5" t="n">
         <v>50</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV5" t="n">
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
         <v>22</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD5" t="n">
         <v>26</v>
       </c>
       <c r="BE5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BK5" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BN5" t="n">
         <v>5</v>
@@ -1814,13 +1814,13 @@
         <v>25</v>
       </c>
       <c r="BS5" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="BT5" t="n">
         <v>7.4</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BV5" t="n">
         <v>29</v>
@@ -1829,10 +1829,10 @@
         <v>10</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
@@ -1903,31 +1903,31 @@
         <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.87</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
         <v>3.2</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
         <v>17</v>
@@ -1936,7 +1936,7 @@
         <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
         <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1966,19 +1966,19 @@
         <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>34</v>
       </c>
       <c r="AM6" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
         <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1987,7 +1987,7 @@
         <v>15</v>
       </c>
       <c r="AR6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS6" t="n">
         <v>70</v>
@@ -1996,13 +1996,13 @@
         <v>9.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
@@ -2014,43 +2014,43 @@
         <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="BB6" t="n">
         <v>20</v>
       </c>
       <c r="BC6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BF6" t="n">
         <v>11.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN6" t="n">
         <v>4.8</v>
@@ -2062,28 +2062,28 @@
         <v>14</v>
       </c>
       <c r="BQ6" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BR6" t="n">
         <v>26</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BT6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BV6" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BX6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>12</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -2127,25 +2127,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G7" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H7" t="n">
         <v>2.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
@@ -2160,16 +2160,16 @@
         <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U7" t="n">
         <v>2.44</v>
@@ -2181,13 +2181,13 @@
         <v>1.64</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
         <v>44</v>
@@ -2199,13 +2199,13 @@
         <v>8.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
@@ -2217,10 +2217,10 @@
         <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
         <v>34</v>
@@ -2229,7 +2229,7 @@
         <v>70</v>
       </c>
       <c r="AN7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO7" t="n">
         <v>22</v>
@@ -2241,7 +2241,7 @@
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
         <v>38</v>
@@ -2271,7 +2271,7 @@
         <v>32</v>
       </c>
       <c r="BB7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
         <v>23</v>
@@ -2280,7 +2280,7 @@
         <v>30</v>
       </c>
       <c r="BE7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF7" t="n">
         <v>16</v>
@@ -2304,7 +2304,7 @@
         <v>90</v>
       </c>
       <c r="BM7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BN7" t="n">
         <v>5.8</v>
@@ -2313,16 +2313,16 @@
         <v>5.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="BR7" t="n">
         <v>28</v>
       </c>
       <c r="BS7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT7" t="n">
         <v>6</v>
@@ -2331,26 +2331,26 @@
         <v>5.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX7" t="n">
         <v>29</v>
       </c>
       <c r="BY7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>21</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -2384,52 +2384,52 @@
         <v>2.82</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H8" t="n">
         <v>2.84</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
         <v>1.38</v>
       </c>
       <c r="P8" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
         <v>1.52</v>
@@ -2486,13 +2486,13 @@
         <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>600</v>
+        <v>55</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>15.5</v>
@@ -2507,7 +2507,7 @@
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
         <v>28</v>
@@ -2516,7 +2516,7 @@
         <v>15.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>15.5</v>
@@ -2528,73 +2528,73 @@
         <v>20</v>
       </c>
       <c r="BC8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD8" t="n">
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF8" t="n">
         <v>27</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BK8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BO8" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>4.9</v>
       </c>
       <c r="BP8" t="n">
         <v>23</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BV8" t="n">
         <v>23</v>
       </c>
       <c r="BW8" t="n">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.88</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.9</v>
-      </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
         <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.47</v>
@@ -2671,22 +2671,22 @@
         <v>2.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S9" t="n">
         <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
         <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X9" t="n">
         <v>12</v>
@@ -2725,10 +2725,10 @@
         <v>200</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AL9" t="n">
         <v>44</v>
@@ -2737,7 +2737,7 @@
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO9" t="n">
         <v>110</v>
@@ -2752,13 +2752,13 @@
         <v>32</v>
       </c>
       <c r="AS9" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AT9" t="n">
         <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
         <v>17.5</v>
@@ -2767,28 +2767,28 @@
         <v>65</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BB9" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BF9" t="n">
         <v>13.5</v>
@@ -2797,25 +2797,25 @@
         <v>80</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BJ9" t="n">
         <v>11</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BO9" t="n">
         <v>3.9</v>
@@ -2824,31 +2824,31 @@
         <v>13.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BR9" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
         <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H10" t="n">
         <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J10" t="n">
         <v>5.4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.17</v>
@@ -2913,28 +2913,28 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O10" t="n">
         <v>1.08</v>
       </c>
       <c r="P10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="R10" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="T10" t="n">
         <v>1.39</v>
       </c>
       <c r="U10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2943,28 +2943,28 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Y10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z10" t="n">
         <v>70</v>
       </c>
       <c r="AA10" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AB10" t="n">
         <v>26</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
         <v>21</v>
@@ -2976,31 +2976,31 @@
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ10" t="n">
         <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AN10" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AO10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AQ10" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AR10" t="n">
         <v>55</v>
@@ -3009,7 +3009,7 @@
         <v>50</v>
       </c>
       <c r="AT10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU10" t="n">
         <v>15</v>
@@ -3021,7 +3021,7 @@
         <v>42</v>
       </c>
       <c r="AX10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AY10" t="n">
         <v>11.5</v>
@@ -3030,43 +3030,43 @@
         <v>14.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BE10" t="n">
         <v>32</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BG10" t="n">
         <v>19.5</v>
       </c>
       <c r="BH10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BI10" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BJ10" t="n">
         <v>9</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL10" t="n">
         <v>48</v>
       </c>
       <c r="BM10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN10" t="n">
         <v>5.6</v>
@@ -3078,31 +3078,31 @@
         <v>9.6</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
         <v>15</v>
       </c>
       <c r="BS10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BT10" t="n">
         <v>10.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BV10" t="n">
         <v>32</v>
       </c>
       <c r="BW10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10" t="n">
         <v>27</v>
       </c>
       <c r="BY10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G11" t="n">
         <v>3.85</v>
       </c>
       <c r="H11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -3167,25 +3167,25 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O11" t="n">
         <v>1.56</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
         <v>1.79</v>
@@ -3203,7 +3203,7 @@
         <v>7.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA11" t="n">
         <v>36</v>
@@ -3212,16 +3212,16 @@
         <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AF11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG11" t="n">
         <v>16</v>
@@ -3230,28 +3230,28 @@
         <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>460</v>
+        <v>150</v>
       </c>
       <c r="AJ11" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AK11" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AL11" t="n">
         <v>500</v>
       </c>
       <c r="AM11" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AN11" t="n">
         <v>110</v>
       </c>
       <c r="AO11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.8</v>
@@ -3266,7 +3266,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>11</v>
@@ -3287,7 +3287,7 @@
         <v>46</v>
       </c>
       <c r="BB11" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BC11" t="n">
         <v>42</v>
@@ -3296,7 +3296,7 @@
         <v>46</v>
       </c>
       <c r="BE11" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BF11" t="n">
         <v>44</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -3397,28 +3397,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="H12" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="I12" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="J12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.45</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
         <v>3.05</v>
@@ -3427,112 +3427,112 @@
         <v>1.46</v>
       </c>
       <c r="P12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
         <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X12" t="n">
         <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG12" t="n">
         <v>20</v>
       </c>
-      <c r="AB12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG12" t="n">
+      <c r="AH12" t="n">
         <v>23</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>25</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
       </c>
       <c r="AJ12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM12" t="n">
         <v>180</v>
       </c>
-      <c r="AK12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>190</v>
-      </c>
       <c r="AN12" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AO12" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AY12" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>21</v>
@@ -3541,31 +3541,31 @@
         <v>44</v>
       </c>
       <c r="BB12" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD12" t="n">
         <v>15</v>
       </c>
-      <c r="BC12" t="n">
-        <v>80</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BE12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI12" t="n">
         <v>2.4</v>
       </c>
       <c r="BJ12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK12" t="n">
         <v>8.6</v>
@@ -3574,53 +3574,53 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BS12" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>65</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>80</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>9.6</v>
       </c>
       <c r="BT12" t="n">
         <v>4.4</v>
       </c>
       <c r="BU12" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BV12" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>36</v>
       </c>
-      <c r="BY12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>34</v>
-      </c>
       <c r="CA12" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -3651,115 +3651,115 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="G13" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="U13" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="V13" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="X13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AD13" t="n">
         <v>30</v>
       </c>
       <c r="AE13" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI13" t="n">
         <v>170</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK13" t="n">
         <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
@@ -3774,7 +3774,7 @@
         <v>4.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
         <v>1.01</v>
@@ -3783,7 +3783,7 @@
         <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
         <v>8.199999999999999</v>
@@ -3813,10 +3813,10 @@
         <v>1.01</v>
       </c>
       <c r="BH13" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BJ13" t="n">
         <v>1000</v>
@@ -3831,10 +3831,10 @@
         <v>1.01</v>
       </c>
       <c r="BN13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="BP13" t="n">
         <v>1000</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="H2" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>200</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S2" t="n">
+        <v>26</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
         <v>1.41</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="X2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>20</v>
       </c>
       <c r="AG2" t="n">
         <v>13</v>
       </c>
       <c r="AH2" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="AL2" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC2" t="n">
         <v>23</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="BD2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="BE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AS2" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>28</v>
-      </c>
       <c r="BG2" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>960</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93</v>
+        <v>1.12</v>
       </c>
       <c r="I3" t="n">
-        <v>1.94</v>
+        <v>1.13</v>
       </c>
       <c r="J3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
         <v>3.45</v>
       </c>
-      <c r="K3" t="n">
+      <c r="Z3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR3" t="n">
         <v>3.55</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AS3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AU3" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AV3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>140</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>170</v>
+      </c>
+      <c r="BE3" t="n">
         <v>80</v>
       </c>
-      <c r="AL3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BF3" t="n">
         <v>70</v>
       </c>
-      <c r="BE3" t="n">
-        <v>120</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>60</v>
-      </c>
       <c r="BG3" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.39</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>18.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>10</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
         <v>4.2</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X4" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AH4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>990</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>44</v>
       </c>
-      <c r="AA4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BH4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB4"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,768 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Brazilian Serie C</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>19:30:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Confianca</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Guarani</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>200</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="S2" t="n">
-        <v>26</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>50</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-22 21:25:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ponte Preta</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>60</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>95</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>100</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>260</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>65</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>75</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>170</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>140</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>170</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>2026-06-22 21:25:39</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Argentinian Torneo A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>20:15:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>9 de Julio Rafaela</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Club Atletico el Linqueno</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>10</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>990</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>44</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
